--- a/resources/rCNV/docs/recurrent_CNV_dataset.xlsx
+++ b/resources/rCNV/docs/recurrent_CNV_dataset.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="420">
   <si>
     <t xml:space="preserve"># This dataset of Region of interest was created using mostly https://www.clinicalgenome.org/ including all Reccurent CNV and adding some gene of interest. Also Some region were Manually Added, see Column Reference</t>
   </si>
@@ -112,9 +112,6 @@
     <t xml:space="preserve">EmergingEvidence</t>
   </si>
   <si>
-    <t xml:space="preserve">10/04/2024</t>
-  </si>
-  <si>
     <t xml:space="preserve">1p36_GABRD</t>
   </si>
   <si>
@@ -136,6 +133,42 @@
     <t xml:space="preserve">1:2019345-2030758</t>
   </si>
   <si>
+    <t xml:space="preserve">2q37_HDAC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">histone deacetylase 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDAC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2q37.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:239969864-240323343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:239048168-239401649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/16/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2q21.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2q21.1 recurrent region (includes ARHGEF4, GPR148)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:131477509-131929693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:130719936-131172120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/13/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">2q13_proximal</t>
   </si>
   <si>
@@ -172,40 +205,34 @@
     <t xml:space="preserve">06/23/2018</t>
   </si>
   <si>
-    <t xml:space="preserve">2q21.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2q21.1 recurrent region (includes ARHGEF4, GPR148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:131477509-131929693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:130719936-131172120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/13/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2q37_HDAC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">histone deacetylase 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDAC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2q37.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:239969864-240323343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:239048168-239401649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/16/2024</t>
+    <t xml:space="preserve">2q11.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2q11.2_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2p11.2 recurrent region (includes EIF2AK3, RPIA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:88295146-89057586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:87995627-88758069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2q11.2_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2q11.2 recurrent region (includes ARID5A, TMEM127)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:96739012-97671429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2:96073264-97005692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/21/2022</t>
   </si>
   <si>
     <t xml:space="preserve">2p16_NRXN1</t>
@@ -226,39 +253,6 @@
     <t xml:space="preserve">2:49918503-51032132</t>
   </si>
   <si>
-    <t xml:space="preserve">2q11.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2q11.2_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2p11.2 recurrent region (includes EIF2AK3, RPIA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:88295146-89057586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:87995627-88758069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/12/2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2q11.2_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2q11.2 recurrent region (includes ARID5A, TMEM127)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:96739012-97671429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2:96073264-97005692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/21/2022</t>
-  </si>
-  <si>
     <t xml:space="preserve">3q29_FGF12</t>
   </si>
   <si>
@@ -295,6 +289,21 @@
     <t xml:space="preserve">02/18/2024</t>
   </si>
   <si>
+    <t xml:space="preserve">4p16.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4p16.3 terminal (Wolf-Hirschhorn syndrome) region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RegionContained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:331568-2010962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4:337779 -2009235</t>
+  </si>
+  <si>
     <t xml:space="preserve">5q35_Ss</t>
   </si>
   <si>
@@ -307,9 +316,6 @@
     <t xml:space="preserve">5:176301976-177620792</t>
   </si>
   <si>
-    <t xml:space="preserve">04/08/2025</t>
-  </si>
-  <si>
     <t xml:space="preserve">6q19_SIM1</t>
   </si>
   <si>
@@ -331,19 +337,31 @@
     <t xml:space="preserve">04/25/2012</t>
   </si>
   <si>
-    <t xml:space="preserve">4p16.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">‐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RegionContained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4p16.3 terminal (Wolf-Hirschhorn syndrome) region</t>
+    <t xml:space="preserve">7q11.23_WBs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7q11.23 recurrent (Williams-Beuren syndrome) region (includes ELN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:72744455-74142510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:73330452-74728172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7q11.23_distal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7q11.23 recurrent distal region (includes HIP1, YWHAG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:75158048-76063176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7:75528718-76433859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/20/2023</t>
   </si>
   <si>
     <t xml:space="preserve">7q11_ZNF92</t>
@@ -364,28 +382,13 @@
     <t xml:space="preserve">7:65373855-65401136</t>
   </si>
   <si>
-    <t xml:space="preserve">7q11.23_WBs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7q11.23 recurrent (Williams-Beuren syndrome) region (includes ELN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:72744455-74142510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:73330452-74728172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2015</t>
-  </si>
-  <si>
     <t xml:space="preserve">7q11_RCC1L</t>
   </si>
   <si>
     <t xml:space="preserve">RCC1 like</t>
   </si>
   <si>
-    <t xml:space="preserve">RCC1L</t>
+    <t xml:space="preserve">RCC1L gne no longer exist</t>
   </si>
   <si>
     <t xml:space="preserve">7q11.23</t>
@@ -397,21 +400,6 @@
     <t xml:space="preserve">7:75027119-75073802</t>
   </si>
   <si>
-    <t xml:space="preserve">7q11.23_distal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7q11.23 recurrent distal region (includes HIP1, YWHAG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:75158048-76063176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7:75528718-76433859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/20/2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">8q22_VPS13B</t>
   </si>
   <si>
@@ -481,6 +469,21 @@
     <t xml:space="preserve">9:841697-969090</t>
   </si>
   <si>
+    <t xml:space="preserve">10q22.3q23.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10q22.3q23.2 recurrent region (includes BMPR1A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:81682843-88739388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:79923087-86979631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/15/2023</t>
+  </si>
+  <si>
     <t xml:space="preserve">10q11.2</t>
   </si>
   <si>
@@ -496,19 +499,19 @@
     <t xml:space="preserve">10/12/2022</t>
   </si>
   <si>
-    <t xml:space="preserve">10q22.3q23.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10q22.3q23.2 recurrent region (includes BMPR1A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:81682843-88739388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:79923087-86979631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/15/2023</t>
+    <t xml:space="preserve">11q13.2q13.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11q13.2q13.4 recurrent region (includes SHANK2, FGFs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:67763646-71236931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:67996175-71525885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/25/2025</t>
   </si>
   <si>
     <t xml:space="preserve">11p11_EXT2</t>
@@ -529,19 +532,19 @@
     <t xml:space="preserve">11:44095678-44251962</t>
   </si>
   <si>
-    <t xml:space="preserve">11q13.2q13.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11q13.2q13.4 recurrent region (includes SHANK2, FGFs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:67763646-71236931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:67996175-71525885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/25/2025</t>
+    <t xml:space="preserve">13q12.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13q12.12 recurrent region (includes SACS, SGCG)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:23544582-24881361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:22970443-24307222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/18/2024</t>
   </si>
   <si>
     <t xml:space="preserve">13q12_ZMYM5</t>
@@ -577,19 +580,37 @@
     <t xml:space="preserve">13:20403669-20525857</t>
   </si>
   <si>
-    <t xml:space="preserve">13q12.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13q12.12 recurrent region (includes SACS, SGCG)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:23544582-24881361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:22970443-24307222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/18/2024</t>
+    <t xml:space="preserve">15q25.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q25.2_proximal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q25.2 recurrent region (proximal, LCR-A/B-C) (includes RPS17)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:83199987-84714733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:82534140-84045981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/18/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q25.2_distal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q25.2q25.3 recurrent region (distal, LCR C-LCR D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:85139652-85713001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:84596421-85169770</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/21/2025</t>
   </si>
   <si>
     <t xml:space="preserve">15q24</t>
@@ -610,6 +631,141 @@
     <t xml:space="preserve">01/13/2020</t>
   </si>
   <si>
+    <t xml:space="preserve">15q24_LCRA_LCRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q24 recurrent region (LCR A-LCR C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:72963715-75508312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:72671374-75215971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/03/2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q24_2_LCRA_LCRD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q24 recurrent region (LCR A-LCR D) (includes SIN3A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:72963715-75972909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:72671374-75680568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/31/2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13.3q14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13.3q14 recurrent region (BP5-BP6) (includes GREM1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:32925116-34671002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:32607508-34378801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13_CHRNA7_BP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13.3 recurrent region (D-CHRNA7 to BP5) (includes CHRNA7, OTUD7A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:32019621-32445405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:31727418-32153204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/10/2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13_BP4_BP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13.3 recurrent region (BP4-BP5) (includes CHRNA7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:31192889-32445405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:30900686-32153204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/28/2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13_BP3_BP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13.3 recurrent region (BP3-BP5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manually_added</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:29156959-32445405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:28916886-32153204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13_BP3_BP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q13 recurrent region (BP3-BP4) (includes APBA2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:29156959-30368990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:28916886-30076787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/11/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q11.2q13_PWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q11.2q13_PWS_BP1_BP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q11.2q13 recurrent (PWS/AS) region (Class I, BP1-BP3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:22832519-28379874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:22782170-28134728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/04/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q11.2q13_PWS_BP2_BP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15q11.2q13 recurrent (PWS/AS) region (Class I, BP1-BP3 and Class II, BP2-BP3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:23747996-28379874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:23465365-28134728</t>
+  </si>
+  <si>
     <t xml:space="preserve">15q11.2</t>
   </si>
   <si>
@@ -625,172 +781,22 @@
     <t xml:space="preserve">04/12/2021</t>
   </si>
   <si>
-    <t xml:space="preserve">15q11.2q13_PWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q11.2q13_PWS_BP1_BP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q11.2q13 recurrent (PWS/AS) region (Class I, BP1-BP3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:22832519-28379874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:22782170-28134728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/04/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q11.2q13_PWS_BP2_BP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q11.2q13 recurrent (PWS/AS) region (Class I, BP1-BP3 and Class II, BP2-BP3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:23747996-28379874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:23465365-28134728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13_BP3_BP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13 recurrent region (BP3-BP4) (includes APBA2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:29156959-30368990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:28916886-30076787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/11/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13_BP3_BP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13.3 recurrent region (BP3-BP5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manually_added</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:29156959-32445405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:28916886-32153204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13_BP4_BP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13.3 recurrent region (BP4-BP5) (includes CHRNA7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:31192889-32445405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:30900686-32153204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/28/2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13_CHRNA7_BP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13.3 recurrent region (D-CHRNA7 to BP5) (includes CHRNA7, OTUD7A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:32019621-32445405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:31727418-32153204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/10/2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13.3q14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q13.3q14 recurrent region (BP5-BP6) (includes GREM1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:32925116-34671002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:32607508-34378801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/09/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q24_LCRA_LCRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q24 recurrent region (LCR A-LCR C)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:72963715-75508312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:72671374-75215971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/03/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q24_2_LCRA_LCRD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q24 recurrent region (LCR A-LCR D) (includes SIN3A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:72963715-75972909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:72671374-75680568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/31/2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q25.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q25.2_proximal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q25.2 recurrent region (proximal, LCR-A/B-C) (includes RPS17)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:83199987-84714733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:82534140-84045981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/18/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q25.2_distal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15q25.2q25.3 recurrent region (distal, LCR C-LCR D)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:85139652-85713001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15:84596421-85169770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/21/2025</t>
+    <t xml:space="preserve">16q23_CDH13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cadherin 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDH13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16q23.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:82660574-83834245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:82626969-83800640</t>
   </si>
   <si>
     <t xml:space="preserve">16p13.11</t>
@@ -808,6 +814,27 @@
     <t xml:space="preserve">08/16/2024</t>
   </si>
   <si>
+    <t xml:space="preserve">16p13_CREBBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREB binding lysine acetyltransferase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREBBP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16p13.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:3775055-3930714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:3725054-3880713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/18/2025</t>
+  </si>
+  <si>
     <t xml:space="preserve">16p12.3</t>
   </si>
   <si>
@@ -823,6 +850,21 @@
     <t xml:space="preserve">06/06/2025</t>
   </si>
   <si>
+    <t xml:space="preserve">16p12.2_proximal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16p12.2 recurrent region (proximal) (includes EEF2K, CDR2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:21948445-22430804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:21937124-22419483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/23/2018</t>
+  </si>
+  <si>
     <t xml:space="preserve">16p12.2_distal</t>
   </si>
   <si>
@@ -835,19 +877,19 @@
     <t xml:space="preserve">16:21558792-21729102</t>
   </si>
   <si>
-    <t xml:space="preserve">16p12.2_proximal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16p12.2 recurrent region (proximal) (includes EEF2K, CDR2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:21948445-22430804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:21937124-22419483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/23/2018</t>
+    <t xml:space="preserve">16p11.2_proximal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16p11.2 recurrent region (proximal, BP4-BP5) (includes TBX6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:29649997-30199852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:29638676-30188531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/09/2017</t>
   </si>
   <si>
     <t xml:space="preserve">16p11.2_distal</t>
@@ -877,58 +919,67 @@
     <t xml:space="preserve">16:28811314-30188531</t>
   </si>
   <si>
-    <t xml:space="preserve">16p11.2_proximal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16p11.2 recurrent region (proximal, BP4-BP5) (includes TBX6)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:29649997-30199852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:29638676-30188531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/09/2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16p13_CREBBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CREB binding lysine acetyltransferase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CREBBP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16p13.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:3775055-3930714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:3725054-3880713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/18/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16q23_CDH13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cadherin 13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDH13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16q23.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:82660574-83834245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:82626969-83800640</t>
+    <t xml:space="preserve">17q23.1q23.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q23.1q23.2 recurrent region (includes TBX2, TBX4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:58113002-60275809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:60035641-62198448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/20/2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q21.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q21.31 recurrent (KdVS) region (includes KANSL1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> undetectable because no geneset identified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:43705166-44164880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:45627800-46087514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/02/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q12_RCADs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q12 recurrent (RCAD syndrome) region (includes HNF1B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:34815072-36192489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:36458167-37854616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/16/2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q11.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17q11.2 recurrent region (includes NF1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:29097069-30264027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30780079-31937008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/12/2020</t>
   </si>
   <si>
     <t xml:space="preserve">17p13_YWHAE</t>
@@ -952,6 +1003,24 @@
     <t xml:space="preserve">06/19/2014</t>
   </si>
   <si>
+    <t xml:space="preserve">17p13_PAFAH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">platelet activating factor acetylhydrolase 1b regulatory subunit 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAFAH1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:2496948-2588909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:2593183-2685615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/13/2020</t>
+  </si>
+  <si>
     <t xml:space="preserve">17p12</t>
   </si>
   <si>
@@ -982,85 +1051,22 @@
     <t xml:space="preserve">11/21/2013</t>
   </si>
   <si>
-    <t xml:space="preserve">17p13_PAFAH1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">platelet activating factor acetylhydrolase 1b regulatory subunit 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAFAH1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:2496948-2588909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:2593183-2685615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/13/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q11.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q11.2 recurrent region (includes NF1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:29097069-30264027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:30780079-31937008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/12/2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q12_RCADs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q12 recurrent (RCAD syndrome) region (includes HNF1B)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:34815072-36192489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:36458167-37854616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/16/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q21.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q21.31 recurrent (KdVS) region (includes KANSL1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> undetectable because no geneset identified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:43705166-44164880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:45627800-46087514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/02/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q23.1q23.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17q23.1q23.2 recurrent region (includes TBX2, TBX4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:58113002-60275809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17:60035641-62198448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/20/2018</t>
+    <t xml:space="preserve">22q13_SHANK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3 and multiple ankyrin repeat domains 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHANK3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22q13.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:51111251-51171640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:50672823-50733212</t>
   </si>
   <si>
     <t xml:space="preserve">22q11.21</t>
@@ -1218,24 +1224,6 @@
     <t xml:space="preserve">09/30/2022</t>
   </si>
   <si>
-    <t xml:space="preserve">22q13_SHANK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3 and multiple ankyrin repeat domains 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHANK3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22q13.33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:51111251-51171640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:50672823-50733212</t>
-  </si>
-  <si>
     <t xml:space="preserve">Xq28_MAGEA11</t>
   </si>
   <si>
@@ -1284,6 +1272,21 @@
     <t xml:space="preserve">X:154890328-155335092</t>
   </si>
   <si>
+    <t xml:space="preserve">Xp22.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xp22.31 recurrent region (includes STS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X:6455812-8124954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X:6537771-8156913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/01/2021</t>
+  </si>
+  <si>
     <t xml:space="preserve">Xp11.22p11.23</t>
   </si>
   <si>
@@ -1297,31 +1300,15 @@
   </si>
   <si>
     <t xml:space="preserve">12/14/2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xp22.31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xp22.31 recurrent region (includes STS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X:6455812-8124954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">X:6537771-8156913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/01/2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="@"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -1434,10 +1421,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1446,16 +1429,12 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1464,6 +1443,14 @@
     </xf>
     <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1575,37 +1562,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1679,7 +1666,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Q1077"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="29.09"/>
@@ -1776,7 +1763,7 @@
       <c r="L3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1811,89 +1798,89 @@
       <c r="L4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>29</v>
+      <c r="M4" s="4" t="n">
+        <v>45392</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" s="5" t="n">
+      <c r="M5" s="4" t="n">
         <v>45116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
+      <c r="G6" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M6" s="1" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>16</v>
@@ -1905,30 +1892,30 @@
         <v>2</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="K7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="1" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>16</v>
@@ -1940,59 +1927,59 @@
         <v>2</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="K8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="L8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="1" t="s">
         <v>53</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="K9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="1" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>61</v>
@@ -2001,39 +1988,39 @@
         <v>62</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H10" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>45635</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>44414</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>16</v>
@@ -2045,100 +2032,100 @@
         <v>2</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="1" t="s">
+      <c r="B12" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="4" t="s">
+      <c r="D12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H12" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>77</v>
+      <c r="M12" s="4" t="n">
+        <v>44414</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M13" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>16</v>
@@ -2150,10 +2137,10 @@
         <v>3</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>27</v>
@@ -2161,158 +2148,162 @@
       <c r="L14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="D15" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>42682</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="7" t="s">
+      <c r="L16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>45873</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="B17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H16" s="7" t="n">
+      <c r="D17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="I16" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="7" t="s">
+      <c r="I17" s="6" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="J17" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D17" s="1" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="B18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="H18" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>42163</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>16</v>
@@ -2324,132 +2315,133 @@
         <v>7</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H20" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="M20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="H21" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="J21" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H22" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="M22" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="M22" s="4" t="n">
         <v>43839</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
-        <v>135</v>
+      <c r="A23" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>16</v>
@@ -2461,10 +2453,10 @@
         <v>8</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>27</v>
@@ -2473,88 +2465,88 @@
         <v>28</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H24" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
+      </c>
+      <c r="M24" s="4" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H25" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="M25" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="M25" s="4" t="n">
         <v>45210</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>152</v>
+      <c r="A26" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>16</v>
@@ -2566,30 +2558,30 @@
         <v>10</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>157</v>
+      <c r="A27" s="5" t="s">
+        <v>153</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>16</v>
@@ -2601,199 +2593,201 @@
         <v>10</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L27" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>162</v>
+      <c r="M27" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>158</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>165</v>
       </c>
       <c r="H28" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>43839</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H29" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>43839</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="D30" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>176</v>
       </c>
       <c r="H30" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H31" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="M31" s="4"/>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>17</v>
+      <c r="G32" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="H32" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="M32" s="4"/>
+    </row>
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>16</v>
@@ -2805,10 +2799,10 @@
         <v>15</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>27</v>
@@ -2816,19 +2810,19 @@
       <c r="L33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>194</v>
+      <c r="M33" s="4" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>195</v>
+      <c r="A34" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>16</v>
@@ -2840,30 +2834,30 @@
         <v>15</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J34" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>16</v>
@@ -2875,24 +2869,30 @@
         <v>15</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>16</v>
@@ -2904,30 +2904,30 @@
         <v>15</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
-        <v>210</v>
+      <c r="A37" s="5" t="s">
+        <v>196</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>16</v>
@@ -2939,56 +2939,65 @@
         <v>15</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M37" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="J37" s="1" t="s">
+      <c r="B38" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="H38" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C39" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>221</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>16</v>
@@ -3000,30 +3009,30 @@
         <v>15</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K39" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>225</v>
+        <v>53</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>16</v>
@@ -3035,65 +3044,57 @@
         <v>15</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K40" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>16</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="H41" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I41" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="M41" s="4"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="J41" s="1" t="s">
+      <c r="B42" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>233</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>16</v>
@@ -3105,30 +3106,30 @@
         <v>15</v>
       </c>
       <c r="I42" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M42" s="4" t="s">
+      <c r="C43" s="1" t="s">
         <v>239</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>241</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>16</v>
@@ -3140,30 +3141,24 @@
         <v>15</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="M43" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="J43" s="1" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="1" t="s">
+      <c r="C44" s="1" t="s">
         <v>244</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>247</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>16</v>
@@ -3175,30 +3170,30 @@
         <v>15</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>250</v>
+        <v>27</v>
+      </c>
+      <c r="M44" s="4" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
-        <v>245</v>
+      <c r="A45" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>16</v>
@@ -3210,65 +3205,63 @@
         <v>15</v>
       </c>
       <c r="I45" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M45" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="J45" s="1" t="s">
+      <c r="D46" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M45" s="1" t="s">
+      <c r="G46" s="1" t="s">
         <v>255</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H46" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="M46" s="4"/>
+    </row>
+    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="J46" s="1" t="s">
+      <c r="B47" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>16</v>
@@ -3280,58 +3273,58 @@
         <v>16</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H48" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="M48" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+    </row>
+    <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
         <v>270</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -3356,12 +3349,12 @@
         <v>273</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M49" s="4" t="s">
         <v>274</v>
       </c>
     </row>
@@ -3391,12 +3384,12 @@
         <v>278</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="4" t="s">
         <v>279</v>
       </c>
     </row>
@@ -3414,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>217</v>
+        <v>17</v>
       </c>
       <c r="H51" s="1" t="n">
         <v>16</v>
@@ -3425,7 +3418,15 @@
       <c r="J51" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="M51" s="4"/>
+      <c r="K51" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
@@ -3473,141 +3474,140 @@
         <v>290</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>292</v>
       </c>
       <c r="H53" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I53" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M53" s="4" t="s">
         <v>293</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>299</v>
+        <v>229</v>
       </c>
       <c r="H54" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I54" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="M54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I55" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J54" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="K55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M55" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C55" s="1" t="s">
+    </row>
+    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="1" t="s">
+      <c r="B56" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="C56" s="9" t="s">
         <v>304</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="D56" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="H55" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I55" s="1" t="s">
+      <c r="G56" s="9"/>
+      <c r="H56" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="I56" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="J55" s="1" t="s">
+      <c r="J56" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="K56" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L56" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="M56" s="10" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B57" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C57" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>315</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>16</v>
@@ -3619,10 +3619,10 @@
         <v>17</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>27</v>
@@ -3630,168 +3630,165 @@
       <c r="L57" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M57" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="58" s="12" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58" s="4" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="58" s="9" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1" t="s">
-        <v>324</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
     </row>
-    <row r="59" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H59" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="M59" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H60" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J60" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="C60" s="1" t="s">
+      <c r="M60" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="D60" s="1" t="s">
+    </row>
+    <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H60" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="K60" s="1" t="s">
+      <c r="E61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H61" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="L61" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M60" s="1" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="61" s="11" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="C61" s="11" t="s">
+      <c r="M61" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="11" t="s">
+    </row>
+    <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="H61" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="I61" s="11" t="s">
+      <c r="B62" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="L61" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="12" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>16</v>
@@ -3803,65 +3800,67 @@
         <v>17</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G63" s="1" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="6" t="s">
+      <c r="H63" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I63" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C63" s="1" t="s">
+      <c r="J63" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="I63" s="1" t="s">
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="4" t="n">
+        <v>43839</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="J63" s="1" t="s">
+      <c r="B64" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>353</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>16</v>
@@ -3873,24 +3872,30 @@
         <v>22</v>
       </c>
       <c r="I64" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="65" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="J64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="M64" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="65" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B65" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>358</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>16</v>
@@ -3898,34 +3903,32 @@
       <c r="E65" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H65" s="7" t="n">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I65" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="66" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B66" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="C66" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="66" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="B66" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>362</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>16</v>
@@ -3933,34 +3936,34 @@
       <c r="E66" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H66" s="7" t="n">
+      <c r="H66" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I66" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="67" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="J66" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M66" s="4" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="67" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>368</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>16</v>
@@ -3968,34 +3971,34 @@
       <c r="E67" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H67" s="7" t="n">
+      <c r="H67" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I67" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="68" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="J67" s="1" t="s">
+      <c r="C68" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="68" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B68" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>16</v>
@@ -4003,34 +4006,34 @@
       <c r="E68" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H68" s="7" t="n">
+      <c r="H68" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="69" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>21</v>
+      </c>
+      <c r="M68" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="69" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B69" s="7" t="s">
-        <v>377</v>
+        <v>368</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>374</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>16</v>
@@ -4038,34 +4041,34 @@
       <c r="E69" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H69" s="7" t="n">
+      <c r="H69" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="70" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="J69" s="1" t="s">
+      <c r="C70" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="70" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B70" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>383</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>16</v>
@@ -4073,34 +4076,34 @@
       <c r="E70" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H70" s="7" t="n">
+      <c r="H70" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M70" s="1" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="71" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M70" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="71" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>366</v>
-      </c>
-      <c r="B71" s="7" t="s">
-        <v>387</v>
+        <v>368</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>384</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>16</v>
@@ -4108,101 +4111,102 @@
       <c r="E71" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H71" s="7" t="n">
+      <c r="H71" s="6" t="n">
         <v>22</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>27</v>
       </c>
       <c r="L71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M71" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="72" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L72" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M71" s="1" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="72" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C72" s="1" t="s">
+      <c r="M72" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" s="1" t="s">
+    </row>
+    <row r="73" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="B73" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="H72" s="7" t="n">
-        <v>22</v>
-      </c>
-      <c r="I72" s="1" t="s">
+      <c r="D73" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F73" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="J72" s="1" t="s">
+      <c r="G73" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="M72" s="5" t="n">
-        <v>43839</v>
-      </c>
-    </row>
-    <row r="73" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="H73" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="C73" s="1" t="s">
+      <c r="I73" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73" s="1" t="s">
+      <c r="J73" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="M73" s="7"/>
+    </row>
+    <row r="74" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="C74" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="74" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>406</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>16</v>
@@ -4211,13 +4215,13 @@
         <v>17</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>20</v>
@@ -4225,19 +4229,19 @@
       <c r="L74" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M74" s="1" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="75" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="6" t="s">
-        <v>401</v>
+      <c r="M74" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="75" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5" t="s">
+        <v>397</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>16</v>
@@ -4246,13 +4250,13 @@
         <v>17</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="K75" s="1" t="s">
         <v>27</v>
@@ -4260,19 +4264,19 @@
       <c r="L75" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M75" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="76" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="6" t="s">
-        <v>414</v>
+      <c r="M75" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5" t="s">
+        <v>410</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>16</v>
@@ -4281,33 +4285,33 @@
         <v>17</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="L76" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="77" s="6" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C77" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L76" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="77" s="7" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>420</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>16</v>
@@ -4316,3172 +4320,3172 @@
         <v>17</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="K77" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L77" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="M77" s="4" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="78" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="78" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C78" s="2"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="9"/>
-    </row>
-    <row r="79" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+    </row>
+    <row r="79" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C79" s="2"/>
     </row>
-    <row r="80" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C80" s="2"/>
     </row>
-    <row r="81" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C81" s="2"/>
     </row>
-    <row r="82" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C82" s="2"/>
     </row>
-    <row r="83" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C83" s="2"/>
     </row>
-    <row r="84" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C84" s="2"/>
     </row>
-    <row r="85" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C85" s="2"/>
     </row>
-    <row r="86" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C86" s="2"/>
     </row>
-    <row r="87" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C87" s="2"/>
     </row>
-    <row r="88" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C88" s="2"/>
     </row>
-    <row r="89" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="14"/>
       <c r="B89" s="14"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
+    <row r="90" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5"/>
+      <c r="B90" s="5"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
+    <row r="91" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5"/>
+      <c r="B91" s="5"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
+    <row r="92" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5"/>
+      <c r="B92" s="5"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
+    <row r="93" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5"/>
+      <c r="B93" s="5"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
+    <row r="94" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5"/>
+      <c r="B94" s="5"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
+    <row r="95" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="5"/>
+      <c r="B95" s="5"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
+    <row r="96" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="5"/>
+      <c r="B96" s="5"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
+    <row r="97" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="5"/>
+      <c r="B97" s="5"/>
       <c r="C97" s="2"/>
     </row>
-    <row r="98" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
+    <row r="98" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="5"/>
+      <c r="B98" s="5"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
+    <row r="99" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5"/>
+      <c r="B99" s="5"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
+    <row r="100" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5"/>
+      <c r="B100" s="5"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
+    <row r="101" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5"/>
+      <c r="B101" s="5"/>
       <c r="C101" s="2"/>
     </row>
-    <row r="102" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
+    <row r="102" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5"/>
+      <c r="B102" s="5"/>
       <c r="C102" s="2"/>
     </row>
-    <row r="103" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
+    <row r="103" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5"/>
+      <c r="B103" s="5"/>
       <c r="C103" s="2"/>
     </row>
-    <row r="104" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
+    <row r="104" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="5"/>
+      <c r="B104" s="5"/>
       <c r="C104" s="2"/>
     </row>
-    <row r="105" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
+    <row r="105" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="5"/>
+      <c r="B105" s="5"/>
       <c r="C105" s="2"/>
     </row>
-    <row r="106" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
+    <row r="106" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5"/>
+      <c r="B106" s="5"/>
       <c r="C106" s="2"/>
     </row>
-    <row r="107" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
+    <row r="107" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="5"/>
+      <c r="B107" s="5"/>
       <c r="C107" s="2"/>
     </row>
-    <row r="108" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
+    <row r="108" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5"/>
+      <c r="B108" s="5"/>
       <c r="C108" s="2"/>
     </row>
-    <row r="109" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
+    <row r="109" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5"/>
+      <c r="B109" s="5"/>
       <c r="C109" s="2"/>
     </row>
-    <row r="110" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
+    <row r="110" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5"/>
+      <c r="B110" s="5"/>
       <c r="C110" s="2"/>
     </row>
-    <row r="111" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
+    <row r="111" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="5"/>
+      <c r="B111" s="5"/>
       <c r="C111" s="2"/>
     </row>
-    <row r="112" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
+    <row r="112" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="5"/>
+      <c r="B112" s="5"/>
       <c r="C112" s="2"/>
     </row>
-    <row r="113" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
+    <row r="113" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="5"/>
+      <c r="B113" s="5"/>
       <c r="C113" s="2"/>
     </row>
-    <row r="114" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
+    <row r="114" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="5"/>
+      <c r="B114" s="5"/>
       <c r="C114" s="2"/>
     </row>
-    <row r="115" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
+    <row r="115" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="5"/>
+      <c r="B115" s="5"/>
       <c r="C115" s="2"/>
     </row>
-    <row r="116" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
+    <row r="116" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="5"/>
+      <c r="B116" s="5"/>
       <c r="C116" s="2"/>
     </row>
-    <row r="117" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
+    <row r="117" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="5"/>
+      <c r="B117" s="5"/>
       <c r="C117" s="2"/>
     </row>
-    <row r="118" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
+    <row r="118" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="5"/>
+      <c r="B118" s="5"/>
       <c r="C118" s="2"/>
     </row>
-    <row r="119" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
+    <row r="119" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="5"/>
+      <c r="B119" s="5"/>
       <c r="C119" s="2"/>
     </row>
-    <row r="120" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
+    <row r="120" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="5"/>
+      <c r="B120" s="5"/>
       <c r="C120" s="2"/>
     </row>
-    <row r="121" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
+    <row r="121" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="5"/>
+      <c r="B121" s="5"/>
       <c r="C121" s="2"/>
     </row>
-    <row r="122" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
+    <row r="122" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="5"/>
+      <c r="B122" s="5"/>
       <c r="C122" s="2"/>
     </row>
-    <row r="123" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
+    <row r="123" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="5"/>
+      <c r="B123" s="5"/>
       <c r="C123" s="2"/>
     </row>
-    <row r="124" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
+    <row r="124" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="5"/>
+      <c r="B124" s="5"/>
       <c r="C124" s="2"/>
     </row>
-    <row r="125" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
+    <row r="125" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="5"/>
+      <c r="B125" s="5"/>
       <c r="C125" s="2"/>
     </row>
-    <row r="126" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
+    <row r="126" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="5"/>
+      <c r="B126" s="5"/>
       <c r="C126" s="2"/>
     </row>
-    <row r="127" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
+    <row r="127" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="5"/>
+      <c r="B127" s="5"/>
       <c r="C127" s="2"/>
     </row>
-    <row r="128" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
+    <row r="128" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="5"/>
+      <c r="B128" s="5"/>
       <c r="C128" s="2"/>
     </row>
-    <row r="129" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
+    <row r="129" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="5"/>
+      <c r="B129" s="5"/>
       <c r="C129" s="2"/>
     </row>
-    <row r="130" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
+    <row r="130" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="5"/>
+      <c r="B130" s="5"/>
       <c r="C130" s="2"/>
     </row>
-    <row r="131" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
+    <row r="131" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="5"/>
+      <c r="B131" s="5"/>
       <c r="C131" s="2"/>
     </row>
-    <row r="132" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
+    <row r="132" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="5"/>
+      <c r="B132" s="5"/>
       <c r="C132" s="2"/>
     </row>
-    <row r="133" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
+    <row r="133" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="5"/>
+      <c r="B133" s="5"/>
       <c r="C133" s="2"/>
     </row>
-    <row r="134" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
+    <row r="134" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="5"/>
+      <c r="B134" s="5"/>
       <c r="C134" s="2"/>
     </row>
-    <row r="135" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
+    <row r="135" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="5"/>
+      <c r="B135" s="5"/>
       <c r="C135" s="2"/>
     </row>
-    <row r="136" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
+    <row r="136" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="5"/>
+      <c r="B136" s="5"/>
       <c r="C136" s="2"/>
     </row>
-    <row r="137" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
+    <row r="137" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="5"/>
+      <c r="B137" s="5"/>
       <c r="C137" s="2"/>
     </row>
-    <row r="138" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
+    <row r="138" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="5"/>
+      <c r="B138" s="5"/>
       <c r="C138" s="2"/>
     </row>
-    <row r="139" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
+    <row r="139" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="5"/>
+      <c r="B139" s="5"/>
       <c r="C139" s="2"/>
     </row>
-    <row r="140" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
+    <row r="140" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="5"/>
+      <c r="B140" s="5"/>
       <c r="C140" s="2"/>
     </row>
-    <row r="141" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
+    <row r="141" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="5"/>
+      <c r="B141" s="5"/>
       <c r="C141" s="2"/>
     </row>
-    <row r="142" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
+    <row r="142" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="5"/>
+      <c r="B142" s="5"/>
       <c r="C142" s="2"/>
     </row>
-    <row r="143" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
+    <row r="143" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="5"/>
+      <c r="B143" s="5"/>
       <c r="C143" s="2"/>
     </row>
-    <row r="144" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
+    <row r="144" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="5"/>
+      <c r="B144" s="5"/>
       <c r="C144" s="2"/>
     </row>
-    <row r="145" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
+    <row r="145" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="5"/>
+      <c r="B145" s="5"/>
       <c r="C145" s="2"/>
     </row>
-    <row r="146" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
+    <row r="146" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="5"/>
+      <c r="B146" s="5"/>
       <c r="C146" s="2"/>
     </row>
-    <row r="147" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
+    <row r="147" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="5"/>
+      <c r="B147" s="5"/>
       <c r="C147" s="2"/>
     </row>
-    <row r="148" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
+    <row r="148" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
       <c r="C148" s="2"/>
     </row>
-    <row r="149" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
+    <row r="149" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="5"/>
+      <c r="B149" s="5"/>
       <c r="C149" s="2"/>
     </row>
-    <row r="150" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
+    <row r="150" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="5"/>
+      <c r="B150" s="5"/>
       <c r="C150" s="2"/>
     </row>
-    <row r="151" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
+    <row r="151" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="5"/>
+      <c r="B151" s="5"/>
       <c r="C151" s="2"/>
     </row>
-    <row r="152" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
+    <row r="152" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="5"/>
+      <c r="B152" s="5"/>
       <c r="C152" s="2"/>
     </row>
-    <row r="153" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
+    <row r="153" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="5"/>
+      <c r="B153" s="5"/>
       <c r="C153" s="2"/>
     </row>
-    <row r="154" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
+    <row r="154" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="5"/>
+      <c r="B154" s="5"/>
       <c r="C154" s="2"/>
     </row>
-    <row r="155" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
+    <row r="155" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="5"/>
+      <c r="B155" s="5"/>
       <c r="C155" s="2"/>
     </row>
-    <row r="156" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
+    <row r="156" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="5"/>
+      <c r="B156" s="5"/>
       <c r="C156" s="2"/>
     </row>
-    <row r="157" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
+    <row r="157" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="5"/>
+      <c r="B157" s="5"/>
       <c r="C157" s="2"/>
     </row>
-    <row r="158" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
+    <row r="158" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="5"/>
+      <c r="B158" s="5"/>
       <c r="C158" s="2"/>
     </row>
-    <row r="159" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
+    <row r="159" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="5"/>
+      <c r="B159" s="5"/>
       <c r="C159" s="2"/>
     </row>
-    <row r="160" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
+    <row r="160" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="5"/>
+      <c r="B160" s="5"/>
       <c r="C160" s="2"/>
     </row>
-    <row r="161" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
+    <row r="161" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="5"/>
+      <c r="B161" s="5"/>
       <c r="C161" s="2"/>
     </row>
-    <row r="162" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
+    <row r="162" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="5"/>
+      <c r="B162" s="5"/>
       <c r="C162" s="2"/>
     </row>
-    <row r="163" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C163" s="2"/>
     </row>
-    <row r="164" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C164" s="2"/>
     </row>
-    <row r="165" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C165" s="2"/>
     </row>
-    <row r="166" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C166" s="2"/>
     </row>
-    <row r="167" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C167" s="2"/>
     </row>
-    <row r="168" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C168" s="2"/>
     </row>
-    <row r="169" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C169" s="2"/>
     </row>
-    <row r="170" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C170" s="2"/>
     </row>
-    <row r="171" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C171" s="2"/>
     </row>
-    <row r="172" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C172" s="2"/>
     </row>
-    <row r="173" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C173" s="2"/>
     </row>
-    <row r="174" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C174" s="2"/>
     </row>
-    <row r="175" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C175" s="2"/>
     </row>
-    <row r="176" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C176" s="2"/>
     </row>
-    <row r="177" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C177" s="2"/>
     </row>
-    <row r="178" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C178" s="2"/>
     </row>
-    <row r="179" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C179" s="2"/>
     </row>
-    <row r="180" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C180" s="2"/>
     </row>
-    <row r="181" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C181" s="2"/>
     </row>
-    <row r="182" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C182" s="2"/>
     </row>
-    <row r="183" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C183" s="2"/>
     </row>
-    <row r="184" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C184" s="2"/>
     </row>
-    <row r="185" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C185" s="2"/>
     </row>
-    <row r="186" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C186" s="2"/>
     </row>
-    <row r="187" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C187" s="2"/>
     </row>
-    <row r="188" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C188" s="2"/>
     </row>
-    <row r="189" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C189" s="2"/>
     </row>
-    <row r="190" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C190" s="2"/>
     </row>
-    <row r="191" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C191" s="2"/>
     </row>
-    <row r="192" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C192" s="2"/>
     </row>
-    <row r="193" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C193" s="2"/>
     </row>
-    <row r="194" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C194" s="2"/>
     </row>
-    <row r="195" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C195" s="2"/>
     </row>
-    <row r="196" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C196" s="2"/>
     </row>
-    <row r="197" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C197" s="2"/>
     </row>
-    <row r="198" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C198" s="2"/>
     </row>
-    <row r="199" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C199" s="2"/>
     </row>
-    <row r="200" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C200" s="2"/>
     </row>
-    <row r="201" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C201" s="2"/>
     </row>
-    <row r="202" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C202" s="2"/>
     </row>
-    <row r="203" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C203" s="2"/>
     </row>
-    <row r="204" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C204" s="2"/>
     </row>
-    <row r="205" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C205" s="2"/>
     </row>
-    <row r="206" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C227" s="2"/>
     </row>
-    <row r="228" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C228" s="2"/>
     </row>
-    <row r="229" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C229" s="2"/>
     </row>
-    <row r="230" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C230" s="2"/>
     </row>
-    <row r="231" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C231" s="2"/>
     </row>
-    <row r="232" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C232" s="2"/>
     </row>
-    <row r="233" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C233" s="2"/>
     </row>
-    <row r="234" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C234" s="2"/>
     </row>
-    <row r="235" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C235" s="2"/>
     </row>
-    <row r="236" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C236" s="2"/>
     </row>
-    <row r="237" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C237" s="2"/>
     </row>
-    <row r="238" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C238" s="2"/>
     </row>
-    <row r="239" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C239" s="2"/>
     </row>
-    <row r="240" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C240" s="2"/>
     </row>
-    <row r="241" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C241" s="2"/>
     </row>
-    <row r="242" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C242" s="2"/>
     </row>
-    <row r="243" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C243" s="2"/>
     </row>
-    <row r="244" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C244" s="2"/>
     </row>
-    <row r="245" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C245" s="2"/>
     </row>
-    <row r="246" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C246" s="2"/>
     </row>
-    <row r="247" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C247" s="2"/>
     </row>
-    <row r="248" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C248" s="2"/>
     </row>
-    <row r="249" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C249" s="2"/>
     </row>
-    <row r="250" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C250" s="2"/>
     </row>
-    <row r="251" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C251" s="2"/>
     </row>
-    <row r="252" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C252" s="2"/>
     </row>
-    <row r="253" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C253" s="2"/>
     </row>
-    <row r="254" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C254" s="2"/>
     </row>
-    <row r="255" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C255" s="2"/>
     </row>
-    <row r="256" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C256" s="2"/>
     </row>
-    <row r="257" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C257" s="2"/>
     </row>
-    <row r="258" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C258" s="2"/>
     </row>
-    <row r="259" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C259" s="2"/>
     </row>
-    <row r="260" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C260" s="2"/>
     </row>
-    <row r="261" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C261" s="2"/>
     </row>
-    <row r="262" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C262" s="2"/>
     </row>
-    <row r="263" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C263" s="2"/>
     </row>
-    <row r="264" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C264" s="2"/>
     </row>
-    <row r="265" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C265" s="2"/>
     </row>
-    <row r="266" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C266" s="2"/>
     </row>
-    <row r="267" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C267" s="2"/>
     </row>
-    <row r="268" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C268" s="2"/>
     </row>
-    <row r="269" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C269" s="2"/>
     </row>
-    <row r="270" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C270" s="2"/>
     </row>
-    <row r="271" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C271" s="2"/>
     </row>
-    <row r="272" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C272" s="2"/>
     </row>
-    <row r="273" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C273" s="2"/>
     </row>
-    <row r="274" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C274" s="2"/>
     </row>
-    <row r="275" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C275" s="2"/>
     </row>
-    <row r="276" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C276" s="2"/>
     </row>
-    <row r="277" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C277" s="2"/>
     </row>
-    <row r="278" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C278" s="2"/>
     </row>
-    <row r="279" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C279" s="2"/>
     </row>
-    <row r="280" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C280" s="2"/>
     </row>
-    <row r="281" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C281" s="2"/>
     </row>
-    <row r="282" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C282" s="2"/>
     </row>
-    <row r="283" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C283" s="2"/>
     </row>
-    <row r="284" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C284" s="2"/>
     </row>
-    <row r="285" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C285" s="2"/>
     </row>
-    <row r="286" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C286" s="2"/>
     </row>
-    <row r="287" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C287" s="2"/>
     </row>
-    <row r="288" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C288" s="2"/>
     </row>
-    <row r="289" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C289" s="2"/>
     </row>
-    <row r="290" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C290" s="2"/>
     </row>
-    <row r="291" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C291" s="2"/>
     </row>
-    <row r="292" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C292" s="2"/>
     </row>
-    <row r="293" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C293" s="2"/>
     </row>
-    <row r="294" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C294" s="2"/>
     </row>
-    <row r="295" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C295" s="2"/>
     </row>
-    <row r="296" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C296" s="2"/>
     </row>
-    <row r="297" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C297" s="2"/>
     </row>
-    <row r="298" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C298" s="2"/>
     </row>
-    <row r="299" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C299" s="2"/>
     </row>
-    <row r="300" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C300" s="2"/>
     </row>
-    <row r="301" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C301" s="2"/>
     </row>
-    <row r="302" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C302" s="2"/>
     </row>
-    <row r="303" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C303" s="2"/>
     </row>
-    <row r="304" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C304" s="2"/>
     </row>
-    <row r="305" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C305" s="2"/>
     </row>
-    <row r="306" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C306" s="2"/>
     </row>
-    <row r="307" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C307" s="2"/>
     </row>
-    <row r="308" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C308" s="2"/>
     </row>
-    <row r="309" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C309" s="2"/>
     </row>
-    <row r="310" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C310" s="2"/>
     </row>
-    <row r="311" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C311" s="2"/>
     </row>
-    <row r="312" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C312" s="2"/>
     </row>
-    <row r="313" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C313" s="2"/>
     </row>
-    <row r="314" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C314" s="2"/>
     </row>
-    <row r="315" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C315" s="2"/>
     </row>
-    <row r="316" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C316" s="2"/>
     </row>
-    <row r="317" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C317" s="2"/>
     </row>
-    <row r="318" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C318" s="2"/>
     </row>
-    <row r="319" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C319" s="2"/>
     </row>
-    <row r="320" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C320" s="2"/>
     </row>
-    <row r="321" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C321" s="2"/>
     </row>
-    <row r="322" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C322" s="2"/>
     </row>
-    <row r="323" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C323" s="2"/>
     </row>
-    <row r="324" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C324" s="2"/>
     </row>
-    <row r="325" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C325" s="2"/>
     </row>
-    <row r="326" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C326" s="2"/>
     </row>
-    <row r="327" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C327" s="2"/>
     </row>
-    <row r="328" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C328" s="2"/>
     </row>
-    <row r="329" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C329" s="2"/>
     </row>
-    <row r="330" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C330" s="2"/>
     </row>
-    <row r="331" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C331" s="2"/>
     </row>
-    <row r="332" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C332" s="2"/>
     </row>
-    <row r="333" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C333" s="2"/>
     </row>
-    <row r="334" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C334" s="2"/>
     </row>
-    <row r="335" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C335" s="2"/>
     </row>
-    <row r="336" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C336" s="2"/>
     </row>
-    <row r="337" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C337" s="2"/>
     </row>
-    <row r="338" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C338" s="2"/>
     </row>
-    <row r="339" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C339" s="2"/>
     </row>
-    <row r="340" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C340" s="2"/>
     </row>
-    <row r="341" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C341" s="2"/>
     </row>
-    <row r="342" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C342" s="2"/>
     </row>
-    <row r="343" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C343" s="2"/>
     </row>
-    <row r="344" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C344" s="2"/>
     </row>
-    <row r="345" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C345" s="2"/>
     </row>
-    <row r="346" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C346" s="2"/>
     </row>
-    <row r="347" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C347" s="2"/>
     </row>
-    <row r="348" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C348" s="2"/>
     </row>
-    <row r="349" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C349" s="2"/>
     </row>
-    <row r="350" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C350" s="2"/>
     </row>
-    <row r="351" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C351" s="2"/>
     </row>
-    <row r="352" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C352" s="2"/>
     </row>
-    <row r="353" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C353" s="2"/>
     </row>
-    <row r="354" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C354" s="2"/>
     </row>
-    <row r="355" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C355" s="2"/>
     </row>
-    <row r="356" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C356" s="2"/>
     </row>
-    <row r="357" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C357" s="2"/>
     </row>
-    <row r="358" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C358" s="2"/>
     </row>
-    <row r="359" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C359" s="2"/>
     </row>
-    <row r="360" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C360" s="2"/>
     </row>
-    <row r="361" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C361" s="2"/>
     </row>
-    <row r="362" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C362" s="2"/>
     </row>
-    <row r="363" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C363" s="2"/>
     </row>
-    <row r="364" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C364" s="2"/>
     </row>
-    <row r="365" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C365" s="2"/>
     </row>
-    <row r="366" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C366" s="2"/>
     </row>
-    <row r="367" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C367" s="2"/>
     </row>
-    <row r="368" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C368" s="2"/>
     </row>
-    <row r="369" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C369" s="2"/>
     </row>
-    <row r="370" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C370" s="2"/>
     </row>
-    <row r="371" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C371" s="2"/>
     </row>
-    <row r="372" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C372" s="2"/>
     </row>
-    <row r="373" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C373" s="2"/>
     </row>
-    <row r="374" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C374" s="2"/>
     </row>
-    <row r="375" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C375" s="2"/>
     </row>
-    <row r="376" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C376" s="2"/>
     </row>
-    <row r="377" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C377" s="2"/>
     </row>
-    <row r="378" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C378" s="2"/>
     </row>
-    <row r="379" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C379" s="2"/>
     </row>
-    <row r="380" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C380" s="2"/>
     </row>
-    <row r="381" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C381" s="2"/>
     </row>
-    <row r="382" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C382" s="2"/>
     </row>
-    <row r="383" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C383" s="2"/>
     </row>
-    <row r="384" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C384" s="2"/>
     </row>
-    <row r="385" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C385" s="2"/>
     </row>
-    <row r="386" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C386" s="2"/>
     </row>
-    <row r="387" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C387" s="2"/>
     </row>
-    <row r="388" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C388" s="2"/>
     </row>
-    <row r="389" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C389" s="2"/>
     </row>
-    <row r="390" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C390" s="2"/>
     </row>
-    <row r="391" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C391" s="2"/>
     </row>
-    <row r="392" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C392" s="2"/>
     </row>
-    <row r="393" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C393" s="2"/>
     </row>
-    <row r="394" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C394" s="2"/>
     </row>
-    <row r="395" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C395" s="2"/>
     </row>
-    <row r="396" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C396" s="2"/>
     </row>
-    <row r="397" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C397" s="2"/>
     </row>
-    <row r="398" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C398" s="2"/>
     </row>
-    <row r="399" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C399" s="2"/>
     </row>
-    <row r="400" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C400" s="2"/>
     </row>
-    <row r="401" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C401" s="2"/>
     </row>
-    <row r="402" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C402" s="2"/>
     </row>
-    <row r="403" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C403" s="2"/>
     </row>
-    <row r="404" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C404" s="2"/>
     </row>
-    <row r="405" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C405" s="2"/>
     </row>
-    <row r="406" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C406" s="2"/>
     </row>
-    <row r="407" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C407" s="2"/>
     </row>
-    <row r="408" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C408" s="2"/>
     </row>
-    <row r="409" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C409" s="2"/>
     </row>
-    <row r="410" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C410" s="2"/>
     </row>
-    <row r="411" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C411" s="2"/>
     </row>
-    <row r="412" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C412" s="2"/>
     </row>
-    <row r="413" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C413" s="2"/>
     </row>
-    <row r="414" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C414" s="2"/>
     </row>
-    <row r="415" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C415" s="2"/>
     </row>
-    <row r="416" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C416" s="2"/>
     </row>
-    <row r="417" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C417" s="2"/>
     </row>
-    <row r="418" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C418" s="2"/>
     </row>
-    <row r="419" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C419" s="2"/>
     </row>
-    <row r="420" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C420" s="2"/>
     </row>
-    <row r="421" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C421" s="2"/>
     </row>
-    <row r="422" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C422" s="2"/>
     </row>
-    <row r="423" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C423" s="2"/>
     </row>
-    <row r="424" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C424" s="2"/>
     </row>
-    <row r="425" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C425" s="2"/>
     </row>
-    <row r="426" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C426" s="2"/>
     </row>
-    <row r="427" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C427" s="2"/>
     </row>
-    <row r="428" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C428" s="2"/>
     </row>
-    <row r="429" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C429" s="2"/>
     </row>
-    <row r="430" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C430" s="2"/>
     </row>
-    <row r="431" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C431" s="2"/>
     </row>
-    <row r="432" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C432" s="2"/>
     </row>
-    <row r="433" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C433" s="2"/>
     </row>
-    <row r="434" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C434" s="2"/>
     </row>
-    <row r="435" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C435" s="2"/>
     </row>
-    <row r="436" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C436" s="2"/>
     </row>
-    <row r="437" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C437" s="2"/>
     </row>
-    <row r="438" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C438" s="2"/>
     </row>
-    <row r="439" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C439" s="2"/>
     </row>
-    <row r="440" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C440" s="2"/>
     </row>
-    <row r="441" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C441" s="2"/>
     </row>
-    <row r="442" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C442" s="2"/>
     </row>
-    <row r="443" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C443" s="2"/>
     </row>
-    <row r="444" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C444" s="2"/>
     </row>
-    <row r="445" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C445" s="2"/>
     </row>
-    <row r="446" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C446" s="2"/>
     </row>
-    <row r="447" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C447" s="2"/>
     </row>
-    <row r="448" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C448" s="2"/>
     </row>
-    <row r="449" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C449" s="2"/>
     </row>
-    <row r="450" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C450" s="2"/>
     </row>
-    <row r="451" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C451" s="2"/>
     </row>
-    <row r="452" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C452" s="2"/>
     </row>
-    <row r="453" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C453" s="2"/>
     </row>
-    <row r="454" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C454" s="2"/>
     </row>
-    <row r="455" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C455" s="2"/>
     </row>
-    <row r="456" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C456" s="2"/>
     </row>
-    <row r="457" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C457" s="2"/>
     </row>
-    <row r="458" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C458" s="2"/>
     </row>
-    <row r="459" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C459" s="2"/>
     </row>
-    <row r="460" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C460" s="2"/>
     </row>
-    <row r="461" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C461" s="2"/>
     </row>
-    <row r="462" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C462" s="2"/>
     </row>
-    <row r="463" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C463" s="2"/>
     </row>
-    <row r="464" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C464" s="2"/>
     </row>
-    <row r="465" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C465" s="2"/>
     </row>
-    <row r="466" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C466" s="2"/>
     </row>
-    <row r="467" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C467" s="2"/>
     </row>
-    <row r="468" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C468" s="2"/>
     </row>
-    <row r="469" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C469" s="2"/>
     </row>
-    <row r="470" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C470" s="2"/>
     </row>
-    <row r="471" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C471" s="2"/>
     </row>
-    <row r="472" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C472" s="2"/>
     </row>
-    <row r="473" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C473" s="2"/>
     </row>
-    <row r="474" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C474" s="2"/>
     </row>
-    <row r="475" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C475" s="2"/>
     </row>
-    <row r="476" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C476" s="2"/>
     </row>
-    <row r="477" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C477" s="2"/>
     </row>
-    <row r="478" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C478" s="2"/>
     </row>
-    <row r="479" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C479" s="2"/>
     </row>
-    <row r="480" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C480" s="2"/>
     </row>
-    <row r="481" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C481" s="2"/>
     </row>
-    <row r="482" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C482" s="2"/>
     </row>
-    <row r="483" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C483" s="2"/>
     </row>
-    <row r="484" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C484" s="2"/>
     </row>
-    <row r="485" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C485" s="2"/>
     </row>
-    <row r="486" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C486" s="2"/>
     </row>
-    <row r="487" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C487" s="2"/>
     </row>
-    <row r="488" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C488" s="2"/>
     </row>
-    <row r="489" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C489" s="2"/>
     </row>
-    <row r="490" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C490" s="2"/>
     </row>
-    <row r="491" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C491" s="2"/>
     </row>
-    <row r="492" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C492" s="2"/>
     </row>
-    <row r="493" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C493" s="2"/>
     </row>
-    <row r="494" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C494" s="2"/>
     </row>
-    <row r="495" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C495" s="2"/>
     </row>
-    <row r="496" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C496" s="2"/>
     </row>
-    <row r="497" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C497" s="2"/>
     </row>
-    <row r="498" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C498" s="2"/>
     </row>
-    <row r="499" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C499" s="2"/>
     </row>
-    <row r="500" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C500" s="2"/>
     </row>
-    <row r="501" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C501" s="2"/>
     </row>
-    <row r="502" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C502" s="2"/>
     </row>
-    <row r="503" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C503" s="2"/>
     </row>
-    <row r="504" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C504" s="2"/>
     </row>
-    <row r="505" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C505" s="2"/>
     </row>
-    <row r="506" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C506" s="2"/>
     </row>
-    <row r="507" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C507" s="2"/>
     </row>
-    <row r="508" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C508" s="2"/>
     </row>
-    <row r="509" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C509" s="2"/>
     </row>
-    <row r="510" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C510" s="2"/>
     </row>
-    <row r="511" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C511" s="2"/>
     </row>
-    <row r="512" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C512" s="2"/>
     </row>
-    <row r="513" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C513" s="2"/>
     </row>
-    <row r="514" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C514" s="2"/>
     </row>
-    <row r="515" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C515" s="2"/>
     </row>
-    <row r="516" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C516" s="2"/>
     </row>
-    <row r="517" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C517" s="2"/>
     </row>
-    <row r="518" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C518" s="2"/>
     </row>
-    <row r="519" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C519" s="2"/>
     </row>
-    <row r="520" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C520" s="2"/>
     </row>
-    <row r="521" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C521" s="2"/>
     </row>
-    <row r="522" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C522" s="2"/>
     </row>
-    <row r="523" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C523" s="2"/>
     </row>
-    <row r="524" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C524" s="2"/>
     </row>
-    <row r="525" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C525" s="2"/>
     </row>
-    <row r="526" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C526" s="2"/>
     </row>
-    <row r="527" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C527" s="2"/>
     </row>
-    <row r="528" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C528" s="2"/>
     </row>
-    <row r="529" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C529" s="2"/>
     </row>
-    <row r="530" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C530" s="2"/>
     </row>
-    <row r="531" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C531" s="2"/>
     </row>
-    <row r="532" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C532" s="2"/>
     </row>
-    <row r="533" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C533" s="2"/>
     </row>
-    <row r="534" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C534" s="2"/>
     </row>
-    <row r="535" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C535" s="2"/>
     </row>
-    <row r="536" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C536" s="2"/>
     </row>
-    <row r="537" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C537" s="2"/>
     </row>
-    <row r="538" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C538" s="2"/>
     </row>
-    <row r="539" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C539" s="2"/>
     </row>
-    <row r="540" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C540" s="2"/>
     </row>
-    <row r="541" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C541" s="2"/>
     </row>
-    <row r="542" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C542" s="2"/>
     </row>
-    <row r="543" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C543" s="2"/>
     </row>
-    <row r="544" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C544" s="2"/>
     </row>
-    <row r="545" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C545" s="2"/>
     </row>
-    <row r="546" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C546" s="2"/>
     </row>
-    <row r="547" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C547" s="2"/>
     </row>
-    <row r="548" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C548" s="2"/>
     </row>
-    <row r="549" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C549" s="2"/>
     </row>
-    <row r="550" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C550" s="2"/>
     </row>
-    <row r="551" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="551" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C551" s="2"/>
     </row>
-    <row r="552" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C552" s="2"/>
     </row>
-    <row r="553" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C553" s="2"/>
     </row>
-    <row r="554" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C554" s="2"/>
     </row>
-    <row r="555" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C555" s="2"/>
     </row>
-    <row r="556" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C556" s="2"/>
     </row>
-    <row r="557" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C557" s="2"/>
     </row>
-    <row r="558" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C558" s="2"/>
     </row>
-    <row r="559" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C559" s="2"/>
     </row>
-    <row r="560" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="560" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C560" s="2"/>
     </row>
-    <row r="561" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C561" s="2"/>
     </row>
-    <row r="562" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="562" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C562" s="2"/>
     </row>
-    <row r="563" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="563" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C563" s="2"/>
     </row>
-    <row r="564" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="564" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C564" s="2"/>
     </row>
-    <row r="565" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C565" s="2"/>
     </row>
-    <row r="566" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="566" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C566" s="2"/>
     </row>
-    <row r="567" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="567" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C567" s="2"/>
     </row>
-    <row r="568" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C568" s="2"/>
     </row>
-    <row r="569" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="569" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C569" s="2"/>
     </row>
-    <row r="570" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C570" s="2"/>
     </row>
-    <row r="571" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="571" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C571" s="2"/>
     </row>
-    <row r="572" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="572" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C572" s="2"/>
     </row>
-    <row r="573" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="573" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C573" s="2"/>
     </row>
-    <row r="574" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C574" s="2"/>
     </row>
-    <row r="575" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C575" s="2"/>
     </row>
-    <row r="576" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="576" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C576" s="2"/>
     </row>
-    <row r="577" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="577" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C577" s="2"/>
     </row>
-    <row r="578" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="578" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C578" s="2"/>
     </row>
-    <row r="579" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="579" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C579" s="2"/>
     </row>
-    <row r="580" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C580" s="2"/>
     </row>
-    <row r="581" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="581" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C581" s="2"/>
     </row>
-    <row r="582" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C582" s="2"/>
     </row>
-    <row r="583" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="583" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C583" s="2"/>
     </row>
-    <row r="584" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="584" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C584" s="2"/>
     </row>
-    <row r="585" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="585" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C585" s="2"/>
     </row>
-    <row r="586" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="586" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C586" s="2"/>
     </row>
-    <row r="587" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="587" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C587" s="2"/>
     </row>
-    <row r="588" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="588" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C588" s="2"/>
     </row>
-    <row r="589" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="589" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C589" s="2"/>
     </row>
-    <row r="590" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="590" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C590" s="2"/>
     </row>
-    <row r="591" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="591" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C591" s="2"/>
     </row>
-    <row r="592" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="592" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C592" s="2"/>
     </row>
-    <row r="593" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="593" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C593" s="2"/>
     </row>
-    <row r="594" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="594" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C594" s="2"/>
     </row>
-    <row r="595" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="595" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C595" s="2"/>
     </row>
-    <row r="596" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="596" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C596" s="2"/>
     </row>
-    <row r="597" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="597" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C597" s="2"/>
     </row>
-    <row r="598" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="598" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C598" s="2"/>
     </row>
-    <row r="599" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="599" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C599" s="2"/>
     </row>
-    <row r="600" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="600" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C600" s="2"/>
     </row>
-    <row r="601" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="601" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C601" s="2"/>
     </row>
-    <row r="602" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="602" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C602" s="2"/>
     </row>
-    <row r="603" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="603" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C603" s="2"/>
     </row>
-    <row r="604" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="604" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C604" s="2"/>
     </row>
-    <row r="605" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="605" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C605" s="2"/>
     </row>
-    <row r="606" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="606" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C606" s="2"/>
     </row>
-    <row r="607" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="607" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C607" s="2"/>
     </row>
-    <row r="608" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="608" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C608" s="2"/>
     </row>
-    <row r="609" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="609" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C609" s="2"/>
     </row>
-    <row r="610" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="610" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C610" s="2"/>
     </row>
-    <row r="611" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="611" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C611" s="2"/>
     </row>
-    <row r="612" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="612" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C612" s="2"/>
     </row>
-    <row r="613" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="613" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C613" s="2"/>
     </row>
-    <row r="614" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="614" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C614" s="2"/>
     </row>
-    <row r="615" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="615" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C615" s="2"/>
     </row>
-    <row r="616" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="616" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C616" s="2"/>
     </row>
-    <row r="617" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="617" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C617" s="2"/>
     </row>
-    <row r="618" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="618" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C618" s="2"/>
     </row>
-    <row r="619" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="619" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C619" s="2"/>
     </row>
-    <row r="620" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="620" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C620" s="2"/>
     </row>
-    <row r="621" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="621" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C621" s="2"/>
     </row>
-    <row r="622" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="622" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C622" s="2"/>
     </row>
-    <row r="623" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="623" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C623" s="2"/>
     </row>
-    <row r="624" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="624" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C624" s="2"/>
     </row>
-    <row r="625" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="625" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C625" s="2"/>
     </row>
-    <row r="626" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="626" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C626" s="2"/>
     </row>
-    <row r="627" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="627" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C627" s="2"/>
     </row>
-    <row r="628" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="628" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C628" s="2"/>
     </row>
-    <row r="629" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="629" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C629" s="2"/>
     </row>
-    <row r="630" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="630" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C630" s="2"/>
     </row>
-    <row r="631" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="631" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C631" s="2"/>
     </row>
-    <row r="632" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="632" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C632" s="2"/>
     </row>
-    <row r="633" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="633" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C633" s="2"/>
     </row>
-    <row r="634" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="634" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C634" s="2"/>
     </row>
-    <row r="635" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="635" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C635" s="2"/>
     </row>
-    <row r="636" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="636" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C636" s="2"/>
     </row>
-    <row r="637" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="637" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C637" s="2"/>
     </row>
-    <row r="638" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="638" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C638" s="2"/>
     </row>
-    <row r="639" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="639" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C639" s="2"/>
     </row>
-    <row r="640" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="640" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C640" s="2"/>
     </row>
-    <row r="641" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="641" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C641" s="2"/>
     </row>
-    <row r="642" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="642" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C642" s="2"/>
     </row>
-    <row r="643" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="643" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C643" s="2"/>
     </row>
-    <row r="644" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="644" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C644" s="2"/>
     </row>
-    <row r="645" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="645" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C645" s="2"/>
     </row>
-    <row r="646" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="646" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C646" s="2"/>
     </row>
-    <row r="647" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="647" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C647" s="2"/>
     </row>
-    <row r="648" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="648" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C648" s="2"/>
     </row>
-    <row r="649" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="649" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C649" s="2"/>
     </row>
-    <row r="650" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="650" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C650" s="2"/>
     </row>
-    <row r="651" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="651" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C651" s="2"/>
     </row>
-    <row r="652" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="652" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C652" s="2"/>
     </row>
-    <row r="653" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="653" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C653" s="2"/>
     </row>
-    <row r="654" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="654" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C654" s="2"/>
     </row>
-    <row r="655" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="655" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C655" s="2"/>
     </row>
-    <row r="656" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="656" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C656" s="2"/>
     </row>
-    <row r="657" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="657" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C657" s="2"/>
     </row>
-    <row r="658" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="658" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C658" s="2"/>
     </row>
-    <row r="659" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="659" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C659" s="2"/>
     </row>
-    <row r="660" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="660" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C660" s="2"/>
     </row>
-    <row r="661" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="661" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C661" s="2"/>
     </row>
-    <row r="662" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="662" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C662" s="2"/>
     </row>
-    <row r="663" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="663" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C663" s="2"/>
     </row>
-    <row r="664" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="664" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C664" s="2"/>
     </row>
-    <row r="665" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="665" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C665" s="2"/>
     </row>
-    <row r="666" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="666" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C666" s="2"/>
     </row>
-    <row r="667" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="667" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C667" s="2"/>
     </row>
-    <row r="668" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C668" s="2"/>
     </row>
-    <row r="669" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="669" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C669" s="2"/>
     </row>
-    <row r="670" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="670" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C670" s="2"/>
     </row>
-    <row r="671" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="671" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C671" s="2"/>
     </row>
-    <row r="672" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="672" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C672" s="2"/>
     </row>
-    <row r="673" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="673" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C673" s="2"/>
     </row>
-    <row r="674" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="674" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C674" s="2"/>
     </row>
-    <row r="675" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="675" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C675" s="2"/>
     </row>
-    <row r="676" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="676" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C676" s="2"/>
     </row>
-    <row r="677" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="677" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C677" s="2"/>
     </row>
-    <row r="678" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="678" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C678" s="2"/>
     </row>
-    <row r="679" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="679" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C679" s="2"/>
     </row>
-    <row r="680" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="680" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C680" s="2"/>
     </row>
-    <row r="681" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="681" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C681" s="2"/>
     </row>
-    <row r="682" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="682" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C682" s="2"/>
     </row>
-    <row r="683" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="683" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C683" s="2"/>
     </row>
-    <row r="684" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="684" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C684" s="2"/>
     </row>
-    <row r="685" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="685" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C685" s="2"/>
     </row>
-    <row r="686" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="686" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C686" s="2"/>
     </row>
-    <row r="687" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="687" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C687" s="2"/>
     </row>
-    <row r="688" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="688" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C688" s="2"/>
     </row>
-    <row r="689" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="689" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C689" s="2"/>
     </row>
-    <row r="690" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="690" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C690" s="2"/>
     </row>
-    <row r="691" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="691" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C691" s="2"/>
     </row>
-    <row r="692" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="692" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C692" s="2"/>
     </row>
-    <row r="693" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="693" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C693" s="2"/>
     </row>
-    <row r="694" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="694" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C694" s="2"/>
     </row>
-    <row r="695" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="695" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C695" s="2"/>
     </row>
-    <row r="696" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="696" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C696" s="2"/>
     </row>
-    <row r="697" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="697" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C697" s="2"/>
     </row>
-    <row r="698" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="698" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C698" s="2"/>
     </row>
-    <row r="699" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="699" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C699" s="2"/>
     </row>
-    <row r="700" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="700" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C700" s="2"/>
     </row>
-    <row r="701" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="701" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C701" s="2"/>
     </row>
-    <row r="702" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="702" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C702" s="2"/>
     </row>
-    <row r="703" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="703" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C703" s="2"/>
     </row>
-    <row r="704" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="704" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C704" s="2"/>
     </row>
-    <row r="705" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="705" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C705" s="2"/>
     </row>
-    <row r="706" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="706" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C706" s="2"/>
     </row>
-    <row r="707" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="707" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C707" s="2"/>
     </row>
-    <row r="708" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="708" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C708" s="2"/>
     </row>
-    <row r="709" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="709" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C709" s="2"/>
     </row>
-    <row r="710" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="710" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C710" s="2"/>
     </row>
-    <row r="711" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="711" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C711" s="2"/>
     </row>
-    <row r="712" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="712" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C712" s="2"/>
     </row>
-    <row r="713" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="713" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C713" s="2"/>
     </row>
-    <row r="714" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="714" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C714" s="2"/>
     </row>
-    <row r="715" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="715" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C715" s="2"/>
     </row>
-    <row r="716" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="716" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C716" s="2"/>
     </row>
-    <row r="717" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="717" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C717" s="2"/>
     </row>
-    <row r="718" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="718" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C718" s="2"/>
     </row>
-    <row r="719" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="719" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C719" s="2"/>
     </row>
-    <row r="720" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="720" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C720" s="2"/>
     </row>
-    <row r="721" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="721" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C721" s="2"/>
     </row>
-    <row r="722" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="722" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C722" s="2"/>
     </row>
-    <row r="723" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="723" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C723" s="2"/>
     </row>
-    <row r="724" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="724" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C724" s="2"/>
     </row>
-    <row r="725" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="725" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C725" s="2"/>
     </row>
-    <row r="726" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="726" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C726" s="2"/>
     </row>
-    <row r="727" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="727" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C727" s="2"/>
     </row>
-    <row r="728" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="728" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C728" s="2"/>
     </row>
-    <row r="729" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="729" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C729" s="2"/>
     </row>
-    <row r="730" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="730" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C730" s="2"/>
     </row>
-    <row r="731" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="731" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C731" s="2"/>
     </row>
-    <row r="732" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="732" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C732" s="2"/>
     </row>
-    <row r="733" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="733" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C733" s="2"/>
     </row>
-    <row r="734" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="734" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C734" s="2"/>
     </row>
-    <row r="735" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="735" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C735" s="2"/>
     </row>
-    <row r="736" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="736" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C736" s="2"/>
     </row>
-    <row r="737" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="737" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C737" s="2"/>
     </row>
-    <row r="738" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="738" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C738" s="2"/>
     </row>
-    <row r="739" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="739" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C739" s="2"/>
     </row>
-    <row r="740" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="740" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C740" s="2"/>
     </row>
-    <row r="741" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="741" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C741" s="2"/>
     </row>
-    <row r="742" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="742" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C742" s="2"/>
     </row>
-    <row r="743" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="743" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C743" s="2"/>
     </row>
-    <row r="744" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="744" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C744" s="2"/>
     </row>
-    <row r="745" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="745" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C745" s="2"/>
     </row>
-    <row r="746" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="746" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C746" s="2"/>
     </row>
-    <row r="747" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="747" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C747" s="2"/>
     </row>
-    <row r="748" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="748" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C748" s="2"/>
     </row>
-    <row r="749" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="749" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C749" s="2"/>
     </row>
-    <row r="750" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="750" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C750" s="2"/>
     </row>
-    <row r="751" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="751" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C751" s="2"/>
     </row>
-    <row r="752" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="752" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C752" s="2"/>
     </row>
-    <row r="753" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="753" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C753" s="2"/>
     </row>
-    <row r="754" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="754" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C754" s="2"/>
     </row>
-    <row r="755" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="755" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C755" s="2"/>
     </row>
-    <row r="756" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="756" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C756" s="2"/>
     </row>
-    <row r="757" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="757" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C757" s="2"/>
     </row>
-    <row r="758" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="758" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C758" s="2"/>
     </row>
-    <row r="759" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="759" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C759" s="2"/>
     </row>
-    <row r="760" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="760" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C760" s="2"/>
     </row>
-    <row r="761" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="761" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C761" s="2"/>
     </row>
-    <row r="762" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="762" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C762" s="2"/>
     </row>
-    <row r="763" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="763" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C763" s="2"/>
     </row>
-    <row r="764" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="764" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C764" s="2"/>
     </row>
-    <row r="765" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="765" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C765" s="2"/>
     </row>
-    <row r="766" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="766" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C766" s="2"/>
     </row>
-    <row r="767" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="767" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C767" s="2"/>
     </row>
-    <row r="768" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="768" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C768" s="2"/>
     </row>
-    <row r="769" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="769" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C769" s="2"/>
     </row>
-    <row r="770" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="770" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C770" s="2"/>
     </row>
-    <row r="771" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="771" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C771" s="2"/>
     </row>
-    <row r="772" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="772" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C772" s="2"/>
     </row>
-    <row r="773" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="773" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C773" s="2"/>
     </row>
-    <row r="774" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="774" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C774" s="2"/>
     </row>
-    <row r="775" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="775" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C775" s="2"/>
     </row>
-    <row r="776" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="776" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C776" s="2"/>
     </row>
-    <row r="777" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="777" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C777" s="2"/>
     </row>
-    <row r="778" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="778" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C778" s="2"/>
     </row>
-    <row r="779" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="779" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C779" s="2"/>
     </row>
-    <row r="780" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="780" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C780" s="2"/>
     </row>
-    <row r="781" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="781" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C781" s="2"/>
     </row>
-    <row r="782" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="782" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C782" s="2"/>
     </row>
-    <row r="783" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="783" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C783" s="2"/>
     </row>
-    <row r="784" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="784" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C784" s="2"/>
     </row>
-    <row r="785" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="785" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C785" s="2"/>
     </row>
-    <row r="786" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="786" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C786" s="2"/>
     </row>
-    <row r="787" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="787" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C787" s="2"/>
     </row>
-    <row r="788" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="788" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C788" s="2"/>
     </row>
-    <row r="789" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="789" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C789" s="2"/>
     </row>
-    <row r="790" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="790" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C790" s="2"/>
     </row>
-    <row r="791" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="791" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C791" s="2"/>
     </row>
-    <row r="792" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="792" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C792" s="2"/>
     </row>
-    <row r="793" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="793" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C793" s="2"/>
     </row>
-    <row r="794" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="794" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C794" s="2"/>
     </row>
-    <row r="795" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="795" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C795" s="2"/>
     </row>
-    <row r="796" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="796" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C796" s="2"/>
     </row>
-    <row r="797" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="797" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C797" s="2"/>
     </row>
-    <row r="798" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="798" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C798" s="2"/>
     </row>
-    <row r="799" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="799" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C799" s="2"/>
     </row>
-    <row r="800" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="800" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C800" s="2"/>
     </row>
-    <row r="801" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="801" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C801" s="2"/>
     </row>
-    <row r="802" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="802" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C802" s="2"/>
     </row>
-    <row r="803" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="803" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C803" s="2"/>
     </row>
-    <row r="804" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="804" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C804" s="2"/>
     </row>
-    <row r="805" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="805" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C805" s="2"/>
     </row>
-    <row r="806" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="806" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C806" s="2"/>
     </row>
-    <row r="807" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="807" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C807" s="2"/>
     </row>
-    <row r="808" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="808" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C808" s="2"/>
     </row>
-    <row r="809" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="809" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C809" s="2"/>
     </row>
-    <row r="810" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="810" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C810" s="2"/>
     </row>
-    <row r="811" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="811" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C811" s="2"/>
     </row>
-    <row r="812" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="812" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C812" s="2"/>
     </row>
-    <row r="813" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="813" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C813" s="2"/>
     </row>
-    <row r="814" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="814" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C814" s="2"/>
     </row>
-    <row r="815" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="815" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C815" s="2"/>
     </row>
-    <row r="816" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="816" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C816" s="2"/>
     </row>
-    <row r="817" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="817" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C817" s="2"/>
     </row>
-    <row r="818" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="818" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C818" s="2"/>
     </row>
-    <row r="819" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="819" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C819" s="2"/>
     </row>
-    <row r="820" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="820" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C820" s="2"/>
     </row>
-    <row r="821" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="821" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C821" s="2"/>
     </row>
-    <row r="822" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="822" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C822" s="2"/>
     </row>
-    <row r="823" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="823" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C823" s="2"/>
     </row>
-    <row r="824" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="824" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C824" s="2"/>
     </row>
-    <row r="825" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="825" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C825" s="2"/>
     </row>
-    <row r="826" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="826" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C826" s="2"/>
     </row>
-    <row r="827" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="827" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C827" s="2"/>
     </row>
-    <row r="828" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="828" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C828" s="2"/>
     </row>
-    <row r="829" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="829" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C829" s="2"/>
     </row>
-    <row r="830" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="830" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C830" s="2"/>
     </row>
-    <row r="831" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="831" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C831" s="2"/>
     </row>
-    <row r="832" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="832" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C832" s="2"/>
     </row>
-    <row r="833" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="833" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C833" s="2"/>
     </row>
-    <row r="834" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="834" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C834" s="2"/>
     </row>
-    <row r="835" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="835" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C835" s="2"/>
     </row>
-    <row r="836" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="836" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C836" s="2"/>
     </row>
-    <row r="837" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="837" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C837" s="2"/>
     </row>
-    <row r="838" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="838" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C838" s="2"/>
     </row>
-    <row r="839" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="839" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C839" s="2"/>
     </row>
-    <row r="840" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="840" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C840" s="2"/>
     </row>
-    <row r="841" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="841" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C841" s="2"/>
     </row>
-    <row r="842" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="842" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C842" s="2"/>
     </row>
-    <row r="843" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="843" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C843" s="2"/>
     </row>
-    <row r="844" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="844" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C844" s="2"/>
     </row>
-    <row r="845" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="845" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C845" s="2"/>
     </row>
-    <row r="846" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="846" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C846" s="2"/>
     </row>
-    <row r="847" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="847" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C847" s="2"/>
     </row>
-    <row r="848" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="848" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C848" s="2"/>
     </row>
-    <row r="849" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="849" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C849" s="2"/>
     </row>
-    <row r="850" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="850" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C850" s="2"/>
     </row>
-    <row r="851" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="851" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C851" s="2"/>
     </row>
-    <row r="852" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="852" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C852" s="2"/>
     </row>
-    <row r="853" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="853" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C853" s="2"/>
     </row>
-    <row r="854" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="854" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C854" s="2"/>
     </row>
-    <row r="855" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="855" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C855" s="2"/>
     </row>
-    <row r="856" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="856" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C856" s="2"/>
     </row>
-    <row r="857" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="857" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C857" s="2"/>
     </row>
-    <row r="858" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="858" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C858" s="2"/>
     </row>
-    <row r="859" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="859" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C859" s="2"/>
     </row>
-    <row r="860" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="860" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C860" s="2"/>
     </row>
-    <row r="861" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="861" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C861" s="2"/>
     </row>
-    <row r="862" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="862" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C862" s="2"/>
     </row>
-    <row r="863" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="863" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C863" s="2"/>
     </row>
-    <row r="864" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="864" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C864" s="2"/>
     </row>
-    <row r="865" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="865" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C865" s="2"/>
     </row>
-    <row r="866" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="866" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C866" s="2"/>
     </row>
-    <row r="867" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="867" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C867" s="2"/>
     </row>
-    <row r="868" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="868" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C868" s="2"/>
     </row>
-    <row r="869" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="869" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C869" s="2"/>
     </row>
-    <row r="870" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="870" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C870" s="2"/>
     </row>
-    <row r="871" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="871" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C871" s="2"/>
     </row>
-    <row r="872" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="872" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C872" s="2"/>
     </row>
-    <row r="873" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="873" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C873" s="2"/>
     </row>
-    <row r="874" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="874" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C874" s="2"/>
     </row>
-    <row r="875" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="875" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C875" s="2"/>
     </row>
-    <row r="876" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="876" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C876" s="2"/>
     </row>
-    <row r="877" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="877" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C877" s="2"/>
     </row>
-    <row r="878" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="878" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C878" s="2"/>
     </row>
-    <row r="879" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="879" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C879" s="2"/>
     </row>
-    <row r="880" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="880" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C880" s="2"/>
     </row>
-    <row r="881" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="881" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C881" s="2"/>
     </row>
-    <row r="882" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="882" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C882" s="2"/>
     </row>
-    <row r="883" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="883" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C883" s="2"/>
     </row>
-    <row r="884" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="884" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C884" s="2"/>
     </row>
-    <row r="885" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="885" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C885" s="2"/>
     </row>
-    <row r="886" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="886" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C886" s="2"/>
     </row>
-    <row r="887" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="887" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C887" s="2"/>
     </row>
-    <row r="888" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="888" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C888" s="2"/>
     </row>
-    <row r="889" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="889" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C889" s="2"/>
     </row>
-    <row r="890" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="890" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C890" s="2"/>
     </row>
-    <row r="891" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="891" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C891" s="2"/>
     </row>
-    <row r="892" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="892" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C892" s="2"/>
     </row>
-    <row r="893" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="893" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C893" s="2"/>
     </row>
-    <row r="894" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="894" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C894" s="2"/>
     </row>
-    <row r="895" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="895" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C895" s="2"/>
     </row>
-    <row r="896" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="896" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C896" s="2"/>
     </row>
-    <row r="897" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="897" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C897" s="2"/>
     </row>
-    <row r="898" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="898" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C898" s="2"/>
     </row>
-    <row r="899" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="899" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C899" s="2"/>
     </row>
-    <row r="900" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="900" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C900" s="2"/>
     </row>
-    <row r="901" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="901" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C901" s="2"/>
     </row>
-    <row r="902" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="902" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C902" s="2"/>
     </row>
-    <row r="903" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="903" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C903" s="2"/>
     </row>
-    <row r="904" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="904" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C904" s="2"/>
     </row>
-    <row r="905" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="905" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C905" s="2"/>
     </row>
-    <row r="906" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="906" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C906" s="2"/>
     </row>
-    <row r="907" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="907" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C907" s="2"/>
     </row>
-    <row r="908" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="908" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C908" s="2"/>
     </row>
-    <row r="909" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="909" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C909" s="2"/>
     </row>
-    <row r="910" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="910" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C910" s="2"/>
     </row>
-    <row r="911" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="911" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C911" s="2"/>
     </row>
-    <row r="912" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="912" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C912" s="2"/>
     </row>
-    <row r="913" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="913" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C913" s="2"/>
     </row>
-    <row r="914" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="914" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C914" s="2"/>
     </row>
-    <row r="915" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="915" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C915" s="2"/>
     </row>
-    <row r="916" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="916" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C916" s="2"/>
     </row>
-    <row r="917" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="917" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C917" s="2"/>
     </row>
-    <row r="918" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="918" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C918" s="2"/>
     </row>
-    <row r="919" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="919" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C919" s="2"/>
     </row>
-    <row r="920" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="920" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C920" s="2"/>
     </row>
-    <row r="921" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="921" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C921" s="2"/>
     </row>
-    <row r="922" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="922" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C922" s="2"/>
     </row>
-    <row r="923" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="923" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C923" s="2"/>
     </row>
-    <row r="924" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="924" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C924" s="2"/>
     </row>
-    <row r="925" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="925" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C925" s="2"/>
     </row>
-    <row r="926" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="926" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C926" s="2"/>
     </row>
-    <row r="927" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="927" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C927" s="2"/>
     </row>
-    <row r="928" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="928" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C928" s="2"/>
     </row>
-    <row r="929" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="929" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C929" s="2"/>
     </row>
-    <row r="930" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="930" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C930" s="2"/>
     </row>
-    <row r="931" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="931" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C931" s="2"/>
     </row>
-    <row r="932" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="932" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C932" s="2"/>
     </row>
-    <row r="933" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="933" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C933" s="2"/>
     </row>
-    <row r="934" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="934" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C934" s="2"/>
     </row>
-    <row r="935" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="935" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C935" s="2"/>
     </row>
-    <row r="936" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="936" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C936" s="2"/>
     </row>
-    <row r="937" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="937" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C937" s="2"/>
     </row>
-    <row r="938" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="938" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C938" s="2"/>
     </row>
-    <row r="939" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="939" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C939" s="2"/>
     </row>
-    <row r="940" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="940" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C940" s="2"/>
     </row>
-    <row r="941" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="941" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C941" s="2"/>
     </row>
-    <row r="942" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="942" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C942" s="2"/>
     </row>
-    <row r="943" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="943" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C943" s="2"/>
     </row>
-    <row r="944" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="944" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C944" s="2"/>
     </row>
-    <row r="945" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="945" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C945" s="2"/>
     </row>
-    <row r="946" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="946" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C946" s="2"/>
     </row>
-    <row r="947" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="947" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C947" s="2"/>
     </row>
-    <row r="948" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="948" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C948" s="2"/>
     </row>
-    <row r="949" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="949" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C949" s="2"/>
     </row>
-    <row r="950" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="950" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C950" s="2"/>
     </row>
-    <row r="951" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="951" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C951" s="2"/>
     </row>
-    <row r="952" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="952" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C952" s="2"/>
     </row>
-    <row r="953" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="953" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C953" s="2"/>
     </row>
-    <row r="954" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="954" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C954" s="2"/>
     </row>
-    <row r="955" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="955" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C955" s="2"/>
     </row>
-    <row r="956" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="956" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C956" s="2"/>
     </row>
-    <row r="957" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="957" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C957" s="2"/>
     </row>
-    <row r="958" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="958" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C958" s="2"/>
     </row>
-    <row r="959" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="959" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C959" s="2"/>
     </row>
-    <row r="960" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="960" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C960" s="2"/>
     </row>
-    <row r="961" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="961" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C961" s="2"/>
     </row>
-    <row r="962" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="962" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C962" s="2"/>
     </row>
-    <row r="963" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="963" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C963" s="2"/>
     </row>
-    <row r="964" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="964" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C964" s="2"/>
     </row>
-    <row r="965" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="965" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C965" s="2"/>
     </row>
-    <row r="966" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="966" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C966" s="2"/>
     </row>
-    <row r="967" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="967" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C967" s="2"/>
     </row>
-    <row r="968" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="968" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C968" s="2"/>
     </row>
-    <row r="969" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="969" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C969" s="2"/>
     </row>
-    <row r="970" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="970" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C970" s="2"/>
     </row>
-    <row r="971" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="971" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C971" s="2"/>
     </row>
-    <row r="972" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="972" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C972" s="2"/>
     </row>
-    <row r="973" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="973" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C973" s="2"/>
     </row>
-    <row r="974" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="974" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C974" s="2"/>
     </row>
-    <row r="975" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="975" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C975" s="2"/>
     </row>
-    <row r="976" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="976" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C976" s="2"/>
     </row>
-    <row r="977" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="977" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C977" s="2"/>
     </row>
-    <row r="978" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="978" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C978" s="2"/>
     </row>
-    <row r="979" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="979" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C979" s="2"/>
     </row>
-    <row r="980" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="980" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C980" s="2"/>
     </row>
-    <row r="981" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="981" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C981" s="2"/>
     </row>
-    <row r="982" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="982" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C982" s="2"/>
     </row>
-    <row r="983" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="983" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C983" s="2"/>
     </row>
-    <row r="984" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="984" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C984" s="2"/>
     </row>
-    <row r="985" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="985" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C985" s="2"/>
     </row>
-    <row r="986" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="986" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C986" s="2"/>
     </row>
-    <row r="987" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="987" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C987" s="2"/>
     </row>
-    <row r="988" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="988" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C988" s="2"/>
     </row>
-    <row r="989" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="989" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C989" s="2"/>
     </row>
-    <row r="990" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="990" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C990" s="2"/>
     </row>
-    <row r="991" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="991" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C991" s="2"/>
     </row>
-    <row r="992" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="992" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C992" s="2"/>
     </row>
-    <row r="993" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="993" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C993" s="2"/>
     </row>
-    <row r="994" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="994" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C994" s="2"/>
     </row>
-    <row r="995" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="995" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C995" s="2"/>
     </row>
-    <row r="996" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="996" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C996" s="2"/>
     </row>
-    <row r="997" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="997" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C997" s="2"/>
     </row>
-    <row r="998" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="998" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C998" s="2"/>
     </row>
-    <row r="999" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="999" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C999" s="2"/>
     </row>
-    <row r="1000" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1000" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1000" s="2"/>
     </row>
-    <row r="1001" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1001" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1001" s="2"/>
     </row>
-    <row r="1002" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1002" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1002" s="2"/>
     </row>
-    <row r="1003" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1003" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1003" s="2"/>
     </row>
-    <row r="1004" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1004" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1004" s="2"/>
     </row>
-    <row r="1005" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1005" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1005" s="2"/>
     </row>
-    <row r="1006" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1006" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1006" s="2"/>
     </row>
-    <row r="1007" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1007" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1007" s="2"/>
     </row>
-    <row r="1008" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1008" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1008" s="2"/>
     </row>
-    <row r="1009" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1009" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1009" s="2"/>
     </row>
-    <row r="1010" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1010" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1010" s="2"/>
     </row>
-    <row r="1011" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1011" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1011" s="2"/>
     </row>
-    <row r="1012" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1012" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1012" s="2"/>
     </row>
-    <row r="1013" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1013" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1013" s="2"/>
     </row>
-    <row r="1014" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1014" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1014" s="2"/>
     </row>
-    <row r="1015" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1015" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1015" s="2"/>
     </row>
-    <row r="1016" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1016" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1016" s="2"/>
     </row>
-    <row r="1017" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1017" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1017" s="2"/>
     </row>
-    <row r="1018" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1018" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1018" s="2"/>
     </row>
-    <row r="1019" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1019" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1019" s="2"/>
     </row>
-    <row r="1020" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1020" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1020" s="2"/>
     </row>
-    <row r="1021" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1021" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1021" s="2"/>
     </row>
-    <row r="1022" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1022" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1022" s="2"/>
     </row>
-    <row r="1023" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1023" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1023" s="2"/>
     </row>
-    <row r="1024" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1024" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1024" s="2"/>
     </row>
-    <row r="1025" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1025" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1025" s="2"/>
     </row>
-    <row r="1026" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1026" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1026" s="2"/>
     </row>
-    <row r="1027" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1027" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1027" s="2"/>
     </row>
-    <row r="1028" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1028" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1028" s="2"/>
     </row>
-    <row r="1029" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1029" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1029" s="2"/>
     </row>
-    <row r="1030" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1030" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1030" s="2"/>
     </row>
-    <row r="1031" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1031" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1031" s="2"/>
     </row>
-    <row r="1032" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1032" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1032" s="2"/>
     </row>
-    <row r="1033" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1033" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1033" s="2"/>
     </row>
-    <row r="1034" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1034" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1034" s="2"/>
     </row>
-    <row r="1035" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1035" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1035" s="2"/>
     </row>
-    <row r="1036" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1036" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1036" s="2"/>
     </row>
-    <row r="1037" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1037" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1037" s="2"/>
     </row>
-    <row r="1038" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1038" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1038" s="2"/>
     </row>
-    <row r="1039" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1039" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1039" s="2"/>
     </row>
-    <row r="1040" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1040" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1040" s="2"/>
     </row>
-    <row r="1041" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1041" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1041" s="2"/>
     </row>
-    <row r="1042" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1042" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1042" s="2"/>
     </row>
-    <row r="1043" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1043" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1043" s="2"/>
     </row>
-    <row r="1044" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1044" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1044" s="2"/>
     </row>
-    <row r="1045" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1045" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1045" s="2"/>
     </row>
-    <row r="1046" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1046" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1046" s="2"/>
     </row>
-    <row r="1047" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1047" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1047" s="2"/>
     </row>
-    <row r="1048" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1048" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1048" s="2"/>
     </row>
-    <row r="1049" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1049" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1049" s="2"/>
     </row>
-    <row r="1050" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1050" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1050" s="2"/>
     </row>
-    <row r="1051" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1051" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1051" s="2"/>
     </row>
-    <row r="1052" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1052" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1052" s="2"/>
     </row>
-    <row r="1053" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1053" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1053" s="2"/>
     </row>
-    <row r="1054" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1054" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1054" s="2"/>
     </row>
-    <row r="1055" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1055" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1055" s="2"/>
     </row>
-    <row r="1056" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1056" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1056" s="2"/>
     </row>
-    <row r="1057" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1057" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1057" s="2"/>
     </row>
-    <row r="1058" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1058" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1058" s="2"/>
     </row>
-    <row r="1059" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1059" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1059" s="2"/>
     </row>
-    <row r="1060" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1060" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1060" s="2"/>
     </row>
-    <row r="1061" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1061" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1061" s="2"/>
     </row>
-    <row r="1062" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1062" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1062" s="2"/>
     </row>
-    <row r="1063" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1063" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1063" s="2"/>
     </row>
-    <row r="1064" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1064" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1064" s="2"/>
     </row>
-    <row r="1065" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1065" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1065" s="2"/>
     </row>
-    <row r="1066" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1066" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1066" s="2"/>
     </row>
-    <row r="1067" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1067" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1067" s="2"/>
     </row>
-    <row r="1068" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1068" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1068" s="2"/>
     </row>
-    <row r="1069" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1069" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1069" s="2"/>
     </row>
-    <row r="1070" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1070" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1070" s="2"/>
     </row>
-    <row r="1071" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1071" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1071" s="2"/>
     </row>
-    <row r="1072" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1072" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1072" s="2"/>
     </row>
-    <row r="1073" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1073" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1073" s="2"/>
     </row>
-    <row r="1074" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1074" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1074" s="2"/>
     </row>
-    <row r="1075" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1075" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1075" s="2"/>
     </row>
-    <row r="1076" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1076" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1076" s="2"/>
     </row>
-    <row r="1077" s="7" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1077" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1077" s="2"/>
     </row>
   </sheetData>
@@ -7490,8 +7494,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/resources/rCNV/docs/recurrent_CNV_dataset.xlsx
+++ b/resources/rCNV/docs/recurrent_CNV_dataset.xlsx
@@ -622,7 +622,7 @@
     <t xml:space="preserve">15q24 recurrent region (LCR C-LCR D) (includes SIN3A)</t>
   </si>
   <si>
-    <t xml:space="preserve">15: 75631787-75972909</t>
+    <t xml:space="preserve">15:75631787-75972909</t>
   </si>
   <si>
     <t xml:space="preserve">15:75339446-75680568</t>
@@ -1296,7 +1296,7 @@
     <t xml:space="preserve">X:48306152-52103258</t>
   </si>
   <si>
-    <t xml:space="preserve">X: 48447780-52444264</t>
+    <t xml:space="preserve">X:48447780-52444264</t>
   </si>
   <si>
     <t xml:space="preserve">12/14/2017</t>

--- a/resources/rCNV/docs/recurrent_CNV_dataset.xlsx
+++ b/resources/rCNV/docs/recurrent_CNV_dataset.xlsx
@@ -1283,7 +1283,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1327,22 +1327,23 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD8CE"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1379,7 +1380,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1400,14 +1401,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1416,7 +1409,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1428,6 +1421,18 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1436,19 +1441,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1461,10 +1458,18 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFD8CE"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1478,6 +1483,66 @@
       </fill>
     </dxf>
   </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFD8CE"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1618,24 +1683,13 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="18" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-    </row>
-    <row r="2" s="5" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="2" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -1677,2048 +1731,1959 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="8" t="n">
+      <c r="K3" s="5"/>
+      <c r="M3" s="6" t="n">
         <v>45116</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="8" t="n">
+      <c r="K4" s="5"/>
+      <c r="M4" s="6" t="n">
         <v>43839</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="8"/>
+      <c r="K5" s="5"/>
+      <c r="M5" s="6"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="6" t="s">
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="8"/>
+      <c r="K6" s="5"/>
+      <c r="M6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="6" t="s">
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="H7" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="8" t="s">
+      <c r="K7" s="5"/>
+      <c r="M7" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="6" t="s">
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="8"/>
+      <c r="K8" s="5"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H9" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="9" t="s">
+      <c r="K9" s="5"/>
+      <c r="M9" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="6" t="s">
+      <c r="E10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I10" s="6" t="s">
+      <c r="H10" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="8" t="s">
+      <c r="K10" s="5"/>
+      <c r="M10" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="H11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="8" t="s">
+      <c r="K11" s="5"/>
+      <c r="M11" s="6" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="6" t="s">
+      <c r="E12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="8" t="s">
+      <c r="K12" s="5"/>
+      <c r="M12" s="6" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="6" t="s">
+      <c r="E13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="10" t="n">
+      <c r="H13" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="J13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="8" t="s">
+      <c r="K13" s="5"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="6" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="6" t="s">
+      <c r="E14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J14" s="6" t="s">
+      <c r="J14" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="8" t="s">
+      <c r="K14" s="5"/>
+      <c r="M14" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="E15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="H15" s="10" t="n">
+      <c r="H15" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="8" t="s">
+      <c r="K15" s="5"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="6" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F16" s="6" t="s">
+      <c r="E16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="8"/>
+      <c r="K16" s="5"/>
+      <c r="M16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="E17" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="H17" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="8"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="8" t="s">
+      <c r="K18" s="5"/>
+      <c r="M18" s="6" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="6" t="s">
+      <c r="E19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="6" t="n">
+      <c r="H19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="8" t="s">
+      <c r="K19" s="5"/>
+      <c r="M19" s="6" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="6" t="s">
+      <c r="E20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="I20" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="8" t="s">
+      <c r="K20" s="5"/>
+      <c r="M20" s="6" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="6" t="s">
+      <c r="E21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="I21" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="J21" s="6" t="s">
+      <c r="J21" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="8"/>
+      <c r="K21" s="5"/>
+      <c r="M21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E22" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6" t="n">
+      <c r="E22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="K22" s="7" t="s">
+      <c r="K22" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L22" s="6" t="s">
+      <c r="L22" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M22" s="8" t="s">
+      <c r="M22" s="6" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6" t="n">
+      <c r="E23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="J23" s="6" t="s">
+      <c r="J23" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L23" s="6" t="s">
+      <c r="L23" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M23" s="8" t="s">
+      <c r="M23" s="6" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6" t="n">
+      <c r="E24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K24" s="7" t="s">
+      <c r="K24" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L24" s="6" t="s">
+      <c r="L24" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="6" t="n">
         <v>44905</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6" t="n">
+      <c r="E25" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="K25" s="7" t="s">
+      <c r="K25" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L25" s="6" t="s">
+      <c r="L25" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M25" s="8" t="s">
+      <c r="M25" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="12" t="s">
+      <c r="A26" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6" t="n">
+      <c r="E26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="K26" s="7" t="s">
+      <c r="K26" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="L26" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M26" s="8" t="s">
+      <c r="M26" s="6" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="6" t="n">
+      <c r="E27" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K27" s="7" t="s">
+      <c r="K27" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M27" s="8" t="s">
+      <c r="M27" s="6" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6" t="n">
+      <c r="E28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="I28" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K28" s="7" t="s">
+      <c r="K28" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="M28" s="8" t="n">
+      <c r="M28" s="6" t="n">
         <v>44534</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
+      <c r="A29" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="6" t="n">
+      <c r="E29" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="I29" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="8" t="n">
+      <c r="K29" s="5"/>
+      <c r="M29" s="6" t="n">
         <v>45755</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6" t="n">
+      <c r="E30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K30" s="7" t="s">
+      <c r="K30" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M30" s="8" t="n">
+      <c r="M30" s="6" t="n">
         <v>45755</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6" t="n">
+      <c r="E31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K31" s="7" t="s">
+      <c r="K31" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L31" s="6" t="s">
+      <c r="L31" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="6" t="n">
         <v>45969</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="E32" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6" t="n">
+      <c r="H32" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="I32" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J32" s="6" t="s">
+      <c r="J32" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="8"/>
+      <c r="K32" s="5"/>
+      <c r="M32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
+      <c r="A33" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6" t="n">
+      <c r="E33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="I33" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="J33" s="6" t="s">
+      <c r="J33" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K33" s="7" t="s">
+      <c r="K33" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L33" s="6" t="s">
+      <c r="L33" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M33" s="8" t="s">
+      <c r="M33" s="6" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6" t="n">
+      <c r="E34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="I34" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J34" s="6" t="s">
+      <c r="J34" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="K34" s="7" t="s">
+      <c r="K34" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="L34" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="M34" s="8" t="s">
+      <c r="M34" s="6" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C35" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6" t="n">
+      <c r="E35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="I35" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="J35" s="6" t="s">
+      <c r="J35" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="K35" s="7" t="s">
+      <c r="K35" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L35" s="6" t="s">
+      <c r="L35" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M35" s="8" t="n">
+      <c r="M35" s="6" t="n">
         <v>45901</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E36" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="6" t="n">
+      <c r="E36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="I36" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="J36" s="6" t="s">
+      <c r="J36" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="K36" s="7" t="s">
+      <c r="K36" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L36" s="6" t="s">
+      <c r="L36" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M36" s="8" t="n">
+      <c r="M36" s="6" t="n">
         <v>43891</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E37" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6" t="n">
+      <c r="E37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="I37" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J37" s="6" t="s">
+      <c r="J37" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="K37" s="7" t="s">
+      <c r="K37" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L37" s="6" t="s">
+      <c r="L37" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M37" s="8" t="s">
+      <c r="M37" s="6" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E38" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="6"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6" t="n">
+      <c r="E38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="I38" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J38" s="6" t="s">
+      <c r="J38" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="K38" s="7" t="s">
+      <c r="K38" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L38" s="6" t="s">
+      <c r="L38" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M38" s="8" t="s">
+      <c r="M38" s="6" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E39" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6" t="n">
+      <c r="E39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="J39" s="6" t="s">
+      <c r="J39" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="K39" s="7" t="s">
+      <c r="K39" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L39" s="6" t="s">
+      <c r="L39" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M39" s="8" t="s">
+      <c r="M39" s="6" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E40" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6" t="n">
+      <c r="E40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H40" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="I40" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="K40" s="7" t="s">
+      <c r="K40" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L40" s="6" t="s">
+      <c r="L40" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M40" s="8" t="s">
+      <c r="M40" s="6" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="12" t="s">
+      <c r="A41" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C41" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="6" t="n">
+      <c r="E41" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="I41" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="J41" s="6" t="s">
+      <c r="J41" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="K41" s="7" t="s">
+      <c r="K41" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L41" s="6" t="s">
+      <c r="L41" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M41" s="8" t="s">
+      <c r="M41" s="6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="12" t="s">
+      <c r="A42" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6" t="n">
+      <c r="E42" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="J42" s="6" t="s">
+      <c r="J42" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K42" s="7" t="s">
+      <c r="K42" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L42" s="6" t="s">
+      <c r="L42" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="6" t="n">
         <v>45814</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6" t="n">
+      <c r="E43" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="I43" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="J43" s="6" t="s">
+      <c r="J43" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="K43" s="7" t="s">
+      <c r="K43" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="L43" s="6" t="s">
+      <c r="L43" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="M43" s="8" t="s">
+      <c r="M43" s="6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6" t="n">
+      <c r="E44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="I44" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="J44" s="6" t="s">
+      <c r="J44" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K44" s="7" t="s">
+      <c r="K44" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L44" s="6" t="s">
+      <c r="L44" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M44" s="8" t="s">
+      <c r="M44" s="6" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C45" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F45" s="6"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="6" t="n">
+      <c r="E45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H45" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="I45" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="J45" s="6" t="s">
+      <c r="J45" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K45" s="7" t="s">
+      <c r="K45" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L45" s="6" t="s">
+      <c r="L45" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M45" s="8" t="s">
+      <c r="M45" s="6" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6" t="n">
+      <c r="H46" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="I46" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J46" s="6" t="s">
+      <c r="J46" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="K46" s="7"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="8"/>
+      <c r="K46" s="5"/>
+      <c r="M46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6" t="n">
+      <c r="E47" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="I47" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="J47" s="6" t="s">
+      <c r="J47" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="K47" s="7" t="s">
+      <c r="K47" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L47" s="6" t="s">
+      <c r="L47" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M47" s="8" t="s">
+      <c r="M47" s="6" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I48" s="6" t="s">
+      <c r="E48" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="J48" s="6" t="s">
+      <c r="J48" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="K48" s="7" t="s">
+      <c r="K48" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L48" s="6" t="s">
+      <c r="L48" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M48" s="8" t="s">
+      <c r="M48" s="6" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="12" t="s">
+      <c r="A49" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="C49" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I49" s="6" t="s">
+      <c r="E49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H49" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J49" s="6" t="s">
+      <c r="J49" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="K49" s="7" t="s">
+      <c r="K49" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L49" s="6" t="s">
+      <c r="L49" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M49" s="8" t="s">
+      <c r="M49" s="6" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E50" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I50" s="6" t="s">
+      <c r="E50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="J50" s="6" t="s">
+      <c r="J50" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="K50" s="7" t="s">
+      <c r="K50" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L50" s="6" t="s">
+      <c r="L50" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M50" s="8" t="n">
+      <c r="M50" s="6" t="n">
         <v>45728</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E51" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I51" s="6" t="s">
+      <c r="E51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J51" s="6" t="s">
+      <c r="J51" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="K51" s="7" t="s">
+      <c r="K51" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L51" s="6" t="s">
+      <c r="L51" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M51" s="8" t="s">
+      <c r="M51" s="6" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="12" t="s">
+      <c r="A52" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="E52" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F52" s="6" t="s">
+      <c r="E52" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="F52" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I52" s="6" t="s">
+      <c r="G52" s="10"/>
+      <c r="H52" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I52" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="J52" s="6" t="s">
+      <c r="J52" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="K52" s="7" t="s">
+      <c r="K52" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="L52" s="6" t="s">
+      <c r="L52" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="M52" s="8" t="n">
+      <c r="M52" s="12" t="n">
         <v>45696</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C53" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I53" s="6" t="s">
+      <c r="E53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H53" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I53" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="J53" s="6" t="s">
+      <c r="J53" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="K53" s="7" t="s">
+      <c r="K53" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L53" s="6" t="s">
+      <c r="L53" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M53" s="8" t="s">
+      <c r="M53" s="6" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="C54" s="6" t="s">
+      <c r="C54" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E54" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6" t="n">
+      <c r="E54" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H54" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="I54" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="J54" s="6" t="s">
+      <c r="J54" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="K54" s="7" t="s">
+      <c r="K54" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="L54" s="6" t="s">
+      <c r="L54" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="M54" s="8" t="s">
+      <c r="M54" s="6" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C55" s="6" t="s">
+      <c r="C55" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E55" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6" t="n">
+      <c r="E55" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="I55" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="J55" s="6" t="s">
+      <c r="J55" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="K55" s="7" t="s">
+      <c r="K55" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L55" s="6" t="s">
+      <c r="L55" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M55" s="8" t="s">
+      <c r="M55" s="6" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="12" t="s">
+      <c r="A56" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="C56" s="6" t="s">
+      <c r="C56" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6" t="n">
+      <c r="E56" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="I56" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="J56" s="6" t="s">
+      <c r="J56" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="K56" s="7" t="s">
+      <c r="K56" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L56" s="6" t="s">
+      <c r="L56" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M56" s="8" t="s">
+      <c r="M56" s="6" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C57" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E57" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6" t="n">
+      <c r="E57" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="I57" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="J57" s="6" t="s">
+      <c r="J57" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="K57" s="7" t="s">
+      <c r="K57" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L57" s="6" t="s">
+      <c r="L57" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M57" s="8" t="n">
+      <c r="M57" s="6" t="n">
         <v>45635</v>
       </c>
     </row>
-    <row r="58" s="13" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="s">
+    <row r="58" s="14" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C58" s="6" t="s">
+      <c r="C58" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E58" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6" t="n">
+      <c r="E58" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="I58" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="J58" s="6" t="s">
+      <c r="J58" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="K58" s="7" t="s">
+      <c r="K58" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L58" s="6" t="s">
+      <c r="L58" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M58" s="8" t="s">
+      <c r="M58" s="6" t="s">
         <v>320</v>
       </c>
       <c r="N58" s="1"/>
@@ -3727,3852 +3692,3832 @@
       <c r="Q58" s="1"/>
     </row>
     <row r="59" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="C59" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6" t="n">
+      <c r="E59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H59" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="I59" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="J59" s="6" t="s">
+      <c r="J59" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="K59" s="7" t="s">
+      <c r="K59" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L59" s="6" t="s">
+      <c r="L59" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M59" s="8" t="s">
+      <c r="M59" s="6" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C60" s="6" t="s">
+      <c r="C60" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E60" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6" t="n">
+      <c r="E60" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H60" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="I60" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="J60" s="6" t="s">
+      <c r="J60" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="K60" s="7"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="8" t="s">
+      <c r="K60" s="5"/>
+      <c r="M60" s="6" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="C61" s="6" t="s">
+      <c r="C61" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10" t="n">
+      <c r="E61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="I61" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="J61" s="6" t="s">
+      <c r="J61" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="K61" s="7" t="s">
+      <c r="K61" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L61" s="6" t="s">
+      <c r="L61" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M61" s="8" t="s">
+      <c r="M61" s="6" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="12" t="s">
+      <c r="A62" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="C62" s="6" t="s">
+      <c r="C62" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E62" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10" t="n">
+      <c r="E62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I62" s="6" t="s">
+      <c r="I62" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="J62" s="6" t="s">
+      <c r="J62" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="K62" s="7" t="s">
+      <c r="K62" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L62" s="6" t="s">
+      <c r="L62" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M62" s="8" t="s">
+      <c r="M62" s="6" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C63" s="6" t="s">
+      <c r="C63" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D63" s="6" t="s">
+      <c r="D63" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E63" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10" t="n">
+      <c r="E63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="I63" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="J63" s="6" t="s">
+      <c r="J63" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K63" s="7" t="s">
+      <c r="K63" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L63" s="6" t="s">
+      <c r="L63" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M63" s="8" t="s">
+      <c r="M63" s="6" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="C64" s="6" t="s">
+      <c r="C64" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="D64" s="6" t="s">
+      <c r="D64" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E64" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10" t="n">
+      <c r="E64" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="I64" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="J64" s="6" t="s">
+      <c r="J64" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="K64" s="7" t="s">
+      <c r="K64" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L64" s="6" t="s">
+      <c r="L64" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="M64" s="8" t="s">
+      <c r="M64" s="6" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="65" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="14" t="s">
+    <row r="65" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="C65" s="6" t="s">
+      <c r="C65" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D65" s="6" t="s">
+      <c r="D65" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E65" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10" t="n">
+      <c r="E65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H65" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I65" s="6" t="s">
+      <c r="I65" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="J65" s="6" t="s">
+      <c r="J65" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="K65" s="7" t="s">
+      <c r="K65" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="L65" s="6" t="s">
+      <c r="L65" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M65" s="8" t="s">
+      <c r="M65" s="6" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="66" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="14" t="s">
+    <row r="66" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="8" t="s">
         <v>356</v>
       </c>
-      <c r="C66" s="6" t="s">
+      <c r="C66" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E66" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10" t="n">
+      <c r="E66" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H66" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I66" s="6" t="s">
+      <c r="I66" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="J66" s="6" t="s">
+      <c r="J66" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="K66" s="7" t="s">
+      <c r="K66" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L66" s="6" t="s">
+      <c r="L66" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M66" s="8" t="s">
+      <c r="M66" s="6" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="67" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="14" t="s">
+    <row r="67" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="8" t="s">
         <v>361</v>
       </c>
-      <c r="C67" s="6" t="s">
+      <c r="C67" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D67" s="6" t="s">
+      <c r="D67" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E67" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10" t="n">
+      <c r="E67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H67" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="I67" s="6" t="s">
+      <c r="I67" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="J67" s="6" t="s">
+      <c r="J67" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="K67" s="7" t="s">
+      <c r="K67" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L67" s="6" t="s">
+      <c r="L67" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M67" s="8" t="s">
+      <c r="M67" s="6" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="68" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="6" t="s">
+    <row r="68" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C68" s="6" t="s">
+      <c r="C68" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D68" s="6" t="s">
+      <c r="D68" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E68" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
-      <c r="H68" s="6" t="n">
+      <c r="E68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I68" s="6" t="s">
+      <c r="I68" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J68" s="6" t="s">
+      <c r="J68" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="K68" s="7" t="s">
+      <c r="K68" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L68" s="6" t="s">
+      <c r="L68" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M68" s="8" t="s">
+      <c r="M68" s="6" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="69" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="12" t="s">
+    <row r="69" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="C69" s="6" t="s">
+      <c r="C69" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D69" s="6" t="s">
+      <c r="D69" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E69" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F69" s="6"/>
-      <c r="G69" s="6"/>
-      <c r="H69" s="6" t="n">
+      <c r="E69" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I69" s="6" t="s">
+      <c r="I69" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="J69" s="6" t="s">
+      <c r="J69" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="K69" s="7" t="s">
+      <c r="K69" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L69" s="6" t="s">
+      <c r="L69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M69" s="8" t="n">
+      <c r="M69" s="6" t="n">
         <v>45873</v>
       </c>
     </row>
-    <row r="70" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="12" t="s">
+    <row r="70" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="C70" s="6" t="s">
+      <c r="C70" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E70" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6" t="n">
+      <c r="E70" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I70" s="6" t="s">
+      <c r="I70" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="J70" s="6" t="s">
+      <c r="J70" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="K70" s="7" t="s">
+      <c r="K70" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L70" s="6" t="s">
+      <c r="L70" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M70" s="8" t="n">
+      <c r="M70" s="6" t="n">
         <v>46114</v>
       </c>
     </row>
-    <row r="71" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="6" t="s">
+    <row r="71" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C71" s="6" t="s">
+      <c r="C71" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D71" s="6" t="s">
+      <c r="D71" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E71" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6" t="n">
+      <c r="E71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="I71" s="6" t="s">
+      <c r="I71" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="J71" s="6" t="s">
+      <c r="J71" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="K71" s="7" t="s">
+      <c r="K71" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="L71" s="6" t="s">
+      <c r="L71" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="M71" s="8" t="s">
+      <c r="M71" s="6" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="72" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12" t="s">
+    <row r="72" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="C72" s="6" t="s">
+      <c r="C72" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D72" s="6" t="s">
+      <c r="D72" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E72" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6" t="n">
+      <c r="E72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="I72" s="6" t="s">
+      <c r="I72" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="J72" s="6" t="s">
+      <c r="J72" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="K72" s="7" t="s">
+      <c r="K72" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L72" s="6" t="s">
+      <c r="L72" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M72" s="8" t="n">
+      <c r="M72" s="6" t="n">
         <v>44840</v>
       </c>
     </row>
-    <row r="73" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12" t="s">
+    <row r="73" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C73" s="6" t="s">
+      <c r="C73" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D73" s="6" t="s">
+      <c r="D73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E73" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73" s="10"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="6" t="s">
+      <c r="E73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I73" s="6" t="s">
+      <c r="I73" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J73" s="6" t="s">
+      <c r="J73" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="K73" s="7" t="s">
+      <c r="K73" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L73" s="6" t="s">
+      <c r="L73" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M73" s="8" t="s">
+      <c r="M73" s="6" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="74" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12" t="s">
+    <row r="74" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="C74" s="6" t="s">
+      <c r="C74" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E74" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F74" s="10"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="6" t="s">
+      <c r="E74" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I74" s="6" t="s">
+      <c r="I74" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="J74" s="6" t="s">
+      <c r="J74" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="K74" s="7" t="s">
+      <c r="K74" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L74" s="6" t="s">
+      <c r="L74" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M74" s="8" t="s">
+      <c r="M74" s="6" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="75" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="s">
+    <row r="75" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C75" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="D75" s="6" t="s">
+      <c r="D75" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E75" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="10"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="6" t="s">
+      <c r="E75" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H75" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I75" s="6" t="s">
+      <c r="I75" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="J75" s="6" t="s">
+      <c r="J75" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="K75" s="7" t="s">
+      <c r="K75" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="L75" s="6" t="s">
+      <c r="L75" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="M75" s="8" t="s">
+      <c r="M75" s="6" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="76" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="12" t="s">
+    <row r="76" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="C76" s="6" t="s">
+      <c r="C76" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="D76" s="6" t="s">
+      <c r="D76" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F76" s="10"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="6" t="s">
+      <c r="E76" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I76" s="6" t="s">
+      <c r="I76" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J76" s="6" t="s">
+      <c r="J76" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="K76" s="7" t="s">
+      <c r="K76" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L76" s="6" t="s">
+      <c r="L76" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="M76" s="8" t="n">
+      <c r="M76" s="6" t="n">
         <v>44203</v>
       </c>
     </row>
-    <row r="77" s="15" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="12" t="s">
+    <row r="77" s="8" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="C77" s="6" t="s">
+      <c r="C77" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D77" s="6" t="s">
+      <c r="D77" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77" s="6"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10" t="n">
+      <c r="E77" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F77" s="1"/>
+      <c r="H77" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="I77" s="6" t="s">
+      <c r="I77" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="J77" s="6" t="s">
+      <c r="J77" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="K77" s="7" t="s">
+      <c r="K77" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L77" s="6" t="s">
+      <c r="L77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="M77" s="8" t="n">
+      <c r="M77" s="6" t="n">
         <v>42682</v>
       </c>
     </row>
-    <row r="78" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C78" s="2"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-    </row>
-    <row r="79" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I78" s="14"/>
+      <c r="J78" s="14"/>
+    </row>
+    <row r="79" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C79" s="2"/>
     </row>
-    <row r="80" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C80" s="2"/>
     </row>
-    <row r="81" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C81" s="2"/>
     </row>
-    <row r="82" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C82" s="2"/>
     </row>
-    <row r="83" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C83" s="2"/>
     </row>
-    <row r="84" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C84" s="2"/>
     </row>
-    <row r="85" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C85" s="2"/>
     </row>
-    <row r="86" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C86" s="2"/>
     </row>
-    <row r="87" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C87" s="2"/>
     </row>
-    <row r="88" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C88" s="2"/>
     </row>
-    <row r="89" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="16"/>
       <c r="B89" s="16"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="17"/>
-      <c r="B90" s="17"/>
+    <row r="90" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="13"/>
+      <c r="B90" s="13"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="17"/>
-      <c r="B91" s="17"/>
+    <row r="91" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="13"/>
+      <c r="B91" s="13"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="17"/>
-      <c r="B92" s="17"/>
+    <row r="92" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="13"/>
+      <c r="B92" s="13"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="17"/>
-      <c r="B93" s="17"/>
+    <row r="93" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="13"/>
+      <c r="B93" s="13"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="17"/>
-      <c r="B94" s="17"/>
+    <row r="94" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="13"/>
+      <c r="B94" s="13"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="17"/>
-      <c r="B95" s="17"/>
+    <row r="95" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="13"/>
+      <c r="B95" s="13"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="17"/>
-      <c r="B96" s="17"/>
+    <row r="96" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="13"/>
+      <c r="B96" s="13"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="17"/>
-      <c r="B97" s="17"/>
+    <row r="97" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="13"/>
+      <c r="B97" s="13"/>
       <c r="C97" s="2"/>
     </row>
-    <row r="98" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="17"/>
-      <c r="B98" s="17"/>
+    <row r="98" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="13"/>
+      <c r="B98" s="13"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="17"/>
-      <c r="B99" s="17"/>
+    <row r="99" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="13"/>
+      <c r="B99" s="13"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="17"/>
-      <c r="B100" s="17"/>
+    <row r="100" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="13"/>
+      <c r="B100" s="13"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="17"/>
-      <c r="B101" s="17"/>
+    <row r="101" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="13"/>
+      <c r="B101" s="13"/>
       <c r="C101" s="2"/>
     </row>
-    <row r="102" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="17"/>
-      <c r="B102" s="17"/>
+    <row r="102" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="13"/>
+      <c r="B102" s="13"/>
       <c r="C102" s="2"/>
     </row>
-    <row r="103" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="17"/>
-      <c r="B103" s="17"/>
+    <row r="103" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="13"/>
+      <c r="B103" s="13"/>
       <c r="C103" s="2"/>
     </row>
-    <row r="104" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="17"/>
-      <c r="B104" s="17"/>
+    <row r="104" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="13"/>
+      <c r="B104" s="13"/>
       <c r="C104" s="2"/>
     </row>
-    <row r="105" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="17"/>
-      <c r="B105" s="17"/>
+    <row r="105" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="13"/>
+      <c r="B105" s="13"/>
       <c r="C105" s="2"/>
     </row>
-    <row r="106" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="17"/>
-      <c r="B106" s="17"/>
+    <row r="106" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="13"/>
+      <c r="B106" s="13"/>
       <c r="C106" s="2"/>
     </row>
-    <row r="107" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="17"/>
-      <c r="B107" s="17"/>
+    <row r="107" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="13"/>
+      <c r="B107" s="13"/>
       <c r="C107" s="2"/>
     </row>
-    <row r="108" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="17"/>
-      <c r="B108" s="17"/>
+    <row r="108" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="13"/>
+      <c r="B108" s="13"/>
       <c r="C108" s="2"/>
     </row>
-    <row r="109" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="17"/>
-      <c r="B109" s="17"/>
+    <row r="109" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="13"/>
+      <c r="B109" s="13"/>
       <c r="C109" s="2"/>
     </row>
-    <row r="110" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="17"/>
-      <c r="B110" s="17"/>
+    <row r="110" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="13"/>
+      <c r="B110" s="13"/>
       <c r="C110" s="2"/>
     </row>
-    <row r="111" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="17"/>
-      <c r="B111" s="17"/>
+    <row r="111" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="13"/>
+      <c r="B111" s="13"/>
       <c r="C111" s="2"/>
     </row>
-    <row r="112" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="17"/>
-      <c r="B112" s="17"/>
+    <row r="112" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="13"/>
+      <c r="B112" s="13"/>
       <c r="C112" s="2"/>
     </row>
-    <row r="113" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="17"/>
-      <c r="B113" s="17"/>
+    <row r="113" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="13"/>
+      <c r="B113" s="13"/>
       <c r="C113" s="2"/>
     </row>
-    <row r="114" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="17"/>
-      <c r="B114" s="17"/>
+    <row r="114" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="13"/>
+      <c r="B114" s="13"/>
       <c r="C114" s="2"/>
     </row>
-    <row r="115" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="17"/>
-      <c r="B115" s="17"/>
+    <row r="115" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="13"/>
+      <c r="B115" s="13"/>
       <c r="C115" s="2"/>
     </row>
-    <row r="116" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="17"/>
-      <c r="B116" s="17"/>
+    <row r="116" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="13"/>
+      <c r="B116" s="13"/>
       <c r="C116" s="2"/>
     </row>
-    <row r="117" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="17"/>
-      <c r="B117" s="17"/>
+    <row r="117" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="13"/>
+      <c r="B117" s="13"/>
       <c r="C117" s="2"/>
     </row>
-    <row r="118" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="17"/>
-      <c r="B118" s="17"/>
+    <row r="118" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="13"/>
+      <c r="B118" s="13"/>
       <c r="C118" s="2"/>
     </row>
-    <row r="119" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="17"/>
-      <c r="B119" s="17"/>
+    <row r="119" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="13"/>
+      <c r="B119" s="13"/>
       <c r="C119" s="2"/>
     </row>
-    <row r="120" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="17"/>
-      <c r="B120" s="17"/>
+    <row r="120" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="13"/>
+      <c r="B120" s="13"/>
       <c r="C120" s="2"/>
     </row>
-    <row r="121" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="17"/>
-      <c r="B121" s="17"/>
+    <row r="121" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="13"/>
+      <c r="B121" s="13"/>
       <c r="C121" s="2"/>
     </row>
-    <row r="122" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="17"/>
-      <c r="B122" s="17"/>
+    <row r="122" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="13"/>
+      <c r="B122" s="13"/>
       <c r="C122" s="2"/>
     </row>
-    <row r="123" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="17"/>
-      <c r="B123" s="17"/>
+    <row r="123" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="13"/>
+      <c r="B123" s="13"/>
       <c r="C123" s="2"/>
     </row>
-    <row r="124" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="17"/>
-      <c r="B124" s="17"/>
+    <row r="124" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="13"/>
+      <c r="B124" s="13"/>
       <c r="C124" s="2"/>
     </row>
-    <row r="125" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="17"/>
-      <c r="B125" s="17"/>
+    <row r="125" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="13"/>
+      <c r="B125" s="13"/>
       <c r="C125" s="2"/>
     </row>
-    <row r="126" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="17"/>
-      <c r="B126" s="17"/>
+    <row r="126" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="13"/>
+      <c r="B126" s="13"/>
       <c r="C126" s="2"/>
     </row>
-    <row r="127" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="17"/>
-      <c r="B127" s="17"/>
+    <row r="127" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="13"/>
+      <c r="B127" s="13"/>
       <c r="C127" s="2"/>
     </row>
-    <row r="128" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="17"/>
-      <c r="B128" s="17"/>
+    <row r="128" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="13"/>
+      <c r="B128" s="13"/>
       <c r="C128" s="2"/>
     </row>
-    <row r="129" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="17"/>
-      <c r="B129" s="17"/>
+    <row r="129" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="13"/>
+      <c r="B129" s="13"/>
       <c r="C129" s="2"/>
     </row>
-    <row r="130" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="17"/>
-      <c r="B130" s="17"/>
+    <row r="130" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="13"/>
+      <c r="B130" s="13"/>
       <c r="C130" s="2"/>
     </row>
-    <row r="131" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="17"/>
-      <c r="B131" s="17"/>
+    <row r="131" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="13"/>
+      <c r="B131" s="13"/>
       <c r="C131" s="2"/>
     </row>
-    <row r="132" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="17"/>
-      <c r="B132" s="17"/>
+    <row r="132" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="13"/>
+      <c r="B132" s="13"/>
       <c r="C132" s="2"/>
     </row>
-    <row r="133" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="17"/>
-      <c r="B133" s="17"/>
+    <row r="133" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="13"/>
+      <c r="B133" s="13"/>
       <c r="C133" s="2"/>
     </row>
-    <row r="134" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="17"/>
-      <c r="B134" s="17"/>
+    <row r="134" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="13"/>
+      <c r="B134" s="13"/>
       <c r="C134" s="2"/>
     </row>
-    <row r="135" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="17"/>
-      <c r="B135" s="17"/>
+    <row r="135" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="13"/>
+      <c r="B135" s="13"/>
       <c r="C135" s="2"/>
     </row>
-    <row r="136" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="17"/>
-      <c r="B136" s="17"/>
+    <row r="136" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="13"/>
+      <c r="B136" s="13"/>
       <c r="C136" s="2"/>
     </row>
-    <row r="137" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="17"/>
-      <c r="B137" s="17"/>
+    <row r="137" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="13"/>
+      <c r="B137" s="13"/>
       <c r="C137" s="2"/>
     </row>
-    <row r="138" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="17"/>
-      <c r="B138" s="17"/>
+    <row r="138" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="13"/>
+      <c r="B138" s="13"/>
       <c r="C138" s="2"/>
     </row>
-    <row r="139" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="17"/>
-      <c r="B139" s="17"/>
+    <row r="139" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="13"/>
+      <c r="B139" s="13"/>
       <c r="C139" s="2"/>
     </row>
-    <row r="140" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="17"/>
-      <c r="B140" s="17"/>
+    <row r="140" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="13"/>
+      <c r="B140" s="13"/>
       <c r="C140" s="2"/>
     </row>
-    <row r="141" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="17"/>
-      <c r="B141" s="17"/>
+    <row r="141" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="13"/>
+      <c r="B141" s="13"/>
       <c r="C141" s="2"/>
     </row>
-    <row r="142" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="17"/>
-      <c r="B142" s="17"/>
+    <row r="142" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="13"/>
+      <c r="B142" s="13"/>
       <c r="C142" s="2"/>
     </row>
-    <row r="143" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="17"/>
-      <c r="B143" s="17"/>
+    <row r="143" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="13"/>
+      <c r="B143" s="13"/>
       <c r="C143" s="2"/>
     </row>
-    <row r="144" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="17"/>
-      <c r="B144" s="17"/>
+    <row r="144" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="13"/>
+      <c r="B144" s="13"/>
       <c r="C144" s="2"/>
     </row>
-    <row r="145" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="17"/>
-      <c r="B145" s="17"/>
+    <row r="145" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="13"/>
+      <c r="B145" s="13"/>
       <c r="C145" s="2"/>
     </row>
-    <row r="146" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="17"/>
-      <c r="B146" s="17"/>
+    <row r="146" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="13"/>
+      <c r="B146" s="13"/>
       <c r="C146" s="2"/>
     </row>
-    <row r="147" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="17"/>
-      <c r="B147" s="17"/>
+    <row r="147" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="13"/>
+      <c r="B147" s="13"/>
       <c r="C147" s="2"/>
     </row>
-    <row r="148" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="17"/>
-      <c r="B148" s="17"/>
+    <row r="148" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="13"/>
+      <c r="B148" s="13"/>
       <c r="C148" s="2"/>
     </row>
-    <row r="149" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="17"/>
-      <c r="B149" s="17"/>
+    <row r="149" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="13"/>
+      <c r="B149" s="13"/>
       <c r="C149" s="2"/>
     </row>
-    <row r="150" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="17"/>
-      <c r="B150" s="17"/>
+    <row r="150" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="13"/>
+      <c r="B150" s="13"/>
       <c r="C150" s="2"/>
     </row>
-    <row r="151" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="17"/>
-      <c r="B151" s="17"/>
+    <row r="151" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="13"/>
+      <c r="B151" s="13"/>
       <c r="C151" s="2"/>
     </row>
-    <row r="152" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="17"/>
-      <c r="B152" s="17"/>
+    <row r="152" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="13"/>
+      <c r="B152" s="13"/>
       <c r="C152" s="2"/>
     </row>
-    <row r="153" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="17"/>
-      <c r="B153" s="17"/>
+    <row r="153" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="13"/>
+      <c r="B153" s="13"/>
       <c r="C153" s="2"/>
     </row>
-    <row r="154" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="17"/>
-      <c r="B154" s="17"/>
+    <row r="154" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="13"/>
+      <c r="B154" s="13"/>
       <c r="C154" s="2"/>
     </row>
-    <row r="155" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="17"/>
-      <c r="B155" s="17"/>
+    <row r="155" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="13"/>
+      <c r="B155" s="13"/>
       <c r="C155" s="2"/>
     </row>
-    <row r="156" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="17"/>
-      <c r="B156" s="17"/>
+    <row r="156" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="13"/>
+      <c r="B156" s="13"/>
       <c r="C156" s="2"/>
     </row>
-    <row r="157" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="17"/>
-      <c r="B157" s="17"/>
+    <row r="157" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="13"/>
+      <c r="B157" s="13"/>
       <c r="C157" s="2"/>
     </row>
-    <row r="158" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="17"/>
-      <c r="B158" s="17"/>
+    <row r="158" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="13"/>
+      <c r="B158" s="13"/>
       <c r="C158" s="2"/>
     </row>
-    <row r="159" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="17"/>
-      <c r="B159" s="17"/>
+    <row r="159" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="13"/>
+      <c r="B159" s="13"/>
       <c r="C159" s="2"/>
     </row>
-    <row r="160" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="17"/>
-      <c r="B160" s="17"/>
+    <row r="160" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="13"/>
+      <c r="B160" s="13"/>
       <c r="C160" s="2"/>
     </row>
-    <row r="161" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="17"/>
-      <c r="B161" s="17"/>
+    <row r="161" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="13"/>
+      <c r="B161" s="13"/>
       <c r="C161" s="2"/>
     </row>
-    <row r="162" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="17"/>
-      <c r="B162" s="17"/>
+    <row r="162" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="13"/>
+      <c r="B162" s="13"/>
       <c r="C162" s="2"/>
     </row>
-    <row r="163" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C163" s="2"/>
     </row>
-    <row r="164" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C164" s="2"/>
     </row>
-    <row r="165" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C165" s="2"/>
     </row>
-    <row r="166" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C166" s="2"/>
     </row>
-    <row r="167" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C167" s="2"/>
     </row>
-    <row r="168" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C168" s="2"/>
     </row>
-    <row r="169" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C169" s="2"/>
     </row>
-    <row r="170" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C170" s="2"/>
     </row>
-    <row r="171" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C171" s="2"/>
     </row>
-    <row r="172" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C172" s="2"/>
     </row>
-    <row r="173" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C173" s="2"/>
     </row>
-    <row r="174" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C174" s="2"/>
     </row>
-    <row r="175" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C175" s="2"/>
     </row>
-    <row r="176" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C176" s="2"/>
     </row>
-    <row r="177" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C177" s="2"/>
     </row>
-    <row r="178" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C178" s="2"/>
     </row>
-    <row r="179" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C179" s="2"/>
     </row>
-    <row r="180" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C180" s="2"/>
     </row>
-    <row r="181" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C181" s="2"/>
     </row>
-    <row r="182" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C182" s="2"/>
     </row>
-    <row r="183" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C183" s="2"/>
     </row>
-    <row r="184" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C184" s="2"/>
     </row>
-    <row r="185" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C185" s="2"/>
     </row>
-    <row r="186" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C186" s="2"/>
     </row>
-    <row r="187" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C187" s="2"/>
     </row>
-    <row r="188" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C188" s="2"/>
     </row>
-    <row r="189" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C189" s="2"/>
     </row>
-    <row r="190" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C190" s="2"/>
     </row>
-    <row r="191" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C191" s="2"/>
     </row>
-    <row r="192" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C192" s="2"/>
     </row>
-    <row r="193" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C193" s="2"/>
     </row>
-    <row r="194" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C194" s="2"/>
     </row>
-    <row r="195" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C195" s="2"/>
     </row>
-    <row r="196" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C196" s="2"/>
     </row>
-    <row r="197" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C197" s="2"/>
     </row>
-    <row r="198" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C198" s="2"/>
     </row>
-    <row r="199" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C199" s="2"/>
     </row>
-    <row r="200" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C200" s="2"/>
     </row>
-    <row r="201" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C201" s="2"/>
     </row>
-    <row r="202" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C202" s="2"/>
     </row>
-    <row r="203" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C203" s="2"/>
     </row>
-    <row r="204" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C204" s="2"/>
     </row>
-    <row r="205" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C205" s="2"/>
     </row>
-    <row r="206" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C206" s="2"/>
     </row>
-    <row r="207" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C207" s="2"/>
     </row>
-    <row r="208" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C208" s="2"/>
     </row>
-    <row r="209" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C209" s="2"/>
     </row>
-    <row r="210" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C210" s="2"/>
     </row>
-    <row r="211" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C211" s="2"/>
     </row>
-    <row r="212" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C212" s="2"/>
     </row>
-    <row r="213" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C213" s="2"/>
     </row>
-    <row r="214" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C214" s="2"/>
     </row>
-    <row r="215" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C215" s="2"/>
     </row>
-    <row r="216" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C216" s="2"/>
     </row>
-    <row r="217" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C217" s="2"/>
     </row>
-    <row r="218" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C218" s="2"/>
     </row>
-    <row r="219" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C219" s="2"/>
     </row>
-    <row r="220" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C220" s="2"/>
     </row>
-    <row r="221" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C221" s="2"/>
     </row>
-    <row r="222" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C222" s="2"/>
     </row>
-    <row r="223" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C223" s="2"/>
     </row>
-    <row r="224" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C224" s="2"/>
     </row>
-    <row r="225" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C225" s="2"/>
     </row>
-    <row r="226" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C226" s="2"/>
     </row>
-    <row r="227" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C227" s="2"/>
     </row>
-    <row r="228" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C228" s="2"/>
     </row>
-    <row r="229" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C229" s="2"/>
     </row>
-    <row r="230" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C230" s="2"/>
     </row>
-    <row r="231" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C231" s="2"/>
     </row>
-    <row r="232" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C232" s="2"/>
     </row>
-    <row r="233" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C233" s="2"/>
     </row>
-    <row r="234" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C234" s="2"/>
     </row>
-    <row r="235" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C235" s="2"/>
     </row>
-    <row r="236" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C236" s="2"/>
     </row>
-    <row r="237" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C237" s="2"/>
     </row>
-    <row r="238" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C238" s="2"/>
     </row>
-    <row r="239" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C239" s="2"/>
     </row>
-    <row r="240" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C240" s="2"/>
     </row>
-    <row r="241" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C241" s="2"/>
     </row>
-    <row r="242" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C242" s="2"/>
     </row>
-    <row r="243" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C243" s="2"/>
     </row>
-    <row r="244" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C244" s="2"/>
     </row>
-    <row r="245" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C245" s="2"/>
     </row>
-    <row r="246" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C246" s="2"/>
     </row>
-    <row r="247" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C247" s="2"/>
     </row>
-    <row r="248" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C248" s="2"/>
     </row>
-    <row r="249" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C249" s="2"/>
     </row>
-    <row r="250" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C250" s="2"/>
     </row>
-    <row r="251" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C251" s="2"/>
     </row>
-    <row r="252" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C252" s="2"/>
     </row>
-    <row r="253" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C253" s="2"/>
     </row>
-    <row r="254" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C254" s="2"/>
     </row>
-    <row r="255" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C255" s="2"/>
     </row>
-    <row r="256" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C256" s="2"/>
     </row>
-    <row r="257" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C257" s="2"/>
     </row>
-    <row r="258" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C258" s="2"/>
     </row>
-    <row r="259" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C259" s="2"/>
     </row>
-    <row r="260" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C260" s="2"/>
     </row>
-    <row r="261" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C261" s="2"/>
     </row>
-    <row r="262" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C262" s="2"/>
     </row>
-    <row r="263" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C263" s="2"/>
     </row>
-    <row r="264" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C264" s="2"/>
     </row>
-    <row r="265" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C265" s="2"/>
     </row>
-    <row r="266" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C266" s="2"/>
     </row>
-    <row r="267" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C267" s="2"/>
     </row>
-    <row r="268" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C268" s="2"/>
     </row>
-    <row r="269" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C269" s="2"/>
     </row>
-    <row r="270" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C270" s="2"/>
     </row>
-    <row r="271" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C271" s="2"/>
     </row>
-    <row r="272" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C272" s="2"/>
     </row>
-    <row r="273" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C273" s="2"/>
     </row>
-    <row r="274" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C274" s="2"/>
     </row>
-    <row r="275" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C275" s="2"/>
     </row>
-    <row r="276" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C276" s="2"/>
     </row>
-    <row r="277" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C277" s="2"/>
     </row>
-    <row r="278" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C278" s="2"/>
     </row>
-    <row r="279" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C279" s="2"/>
     </row>
-    <row r="280" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C280" s="2"/>
     </row>
-    <row r="281" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C281" s="2"/>
     </row>
-    <row r="282" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C282" s="2"/>
     </row>
-    <row r="283" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C283" s="2"/>
     </row>
-    <row r="284" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C284" s="2"/>
     </row>
-    <row r="285" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C285" s="2"/>
     </row>
-    <row r="286" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C286" s="2"/>
     </row>
-    <row r="287" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C287" s="2"/>
     </row>
-    <row r="288" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C288" s="2"/>
     </row>
-    <row r="289" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C289" s="2"/>
     </row>
-    <row r="290" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C290" s="2"/>
     </row>
-    <row r="291" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C291" s="2"/>
     </row>
-    <row r="292" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C292" s="2"/>
     </row>
-    <row r="293" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C293" s="2"/>
     </row>
-    <row r="294" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C294" s="2"/>
     </row>
-    <row r="295" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C295" s="2"/>
     </row>
-    <row r="296" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C296" s="2"/>
     </row>
-    <row r="297" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C297" s="2"/>
     </row>
-    <row r="298" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C298" s="2"/>
     </row>
-    <row r="299" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C299" s="2"/>
     </row>
-    <row r="300" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C300" s="2"/>
     </row>
-    <row r="301" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C301" s="2"/>
     </row>
-    <row r="302" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C302" s="2"/>
     </row>
-    <row r="303" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C303" s="2"/>
     </row>
-    <row r="304" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C304" s="2"/>
     </row>
-    <row r="305" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C305" s="2"/>
     </row>
-    <row r="306" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C306" s="2"/>
     </row>
-    <row r="307" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C307" s="2"/>
     </row>
-    <row r="308" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C308" s="2"/>
     </row>
-    <row r="309" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C309" s="2"/>
     </row>
-    <row r="310" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C310" s="2"/>
     </row>
-    <row r="311" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C311" s="2"/>
     </row>
-    <row r="312" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C312" s="2"/>
     </row>
-    <row r="313" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C313" s="2"/>
     </row>
-    <row r="314" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C314" s="2"/>
     </row>
-    <row r="315" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C315" s="2"/>
     </row>
-    <row r="316" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C316" s="2"/>
     </row>
-    <row r="317" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C317" s="2"/>
     </row>
-    <row r="318" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C318" s="2"/>
     </row>
-    <row r="319" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C319" s="2"/>
     </row>
-    <row r="320" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C320" s="2"/>
     </row>
-    <row r="321" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C321" s="2"/>
     </row>
-    <row r="322" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C322" s="2"/>
     </row>
-    <row r="323" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C323" s="2"/>
     </row>
-    <row r="324" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C324" s="2"/>
     </row>
-    <row r="325" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C325" s="2"/>
     </row>
-    <row r="326" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C326" s="2"/>
     </row>
-    <row r="327" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C327" s="2"/>
     </row>
-    <row r="328" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C328" s="2"/>
     </row>
-    <row r="329" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C329" s="2"/>
     </row>
-    <row r="330" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C330" s="2"/>
     </row>
-    <row r="331" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C331" s="2"/>
     </row>
-    <row r="332" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C332" s="2"/>
     </row>
-    <row r="333" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C333" s="2"/>
     </row>
-    <row r="334" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C334" s="2"/>
     </row>
-    <row r="335" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C335" s="2"/>
     </row>
-    <row r="336" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C336" s="2"/>
     </row>
-    <row r="337" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C337" s="2"/>
     </row>
-    <row r="338" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C338" s="2"/>
     </row>
-    <row r="339" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C339" s="2"/>
     </row>
-    <row r="340" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C340" s="2"/>
     </row>
-    <row r="341" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C341" s="2"/>
     </row>
-    <row r="342" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C342" s="2"/>
     </row>
-    <row r="343" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C343" s="2"/>
     </row>
-    <row r="344" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C344" s="2"/>
     </row>
-    <row r="345" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C345" s="2"/>
     </row>
-    <row r="346" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C346" s="2"/>
     </row>
-    <row r="347" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C347" s="2"/>
     </row>
-    <row r="348" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C348" s="2"/>
     </row>
-    <row r="349" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C349" s="2"/>
     </row>
-    <row r="350" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C350" s="2"/>
     </row>
-    <row r="351" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C351" s="2"/>
     </row>
-    <row r="352" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C352" s="2"/>
     </row>
-    <row r="353" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C353" s="2"/>
     </row>
-    <row r="354" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C354" s="2"/>
     </row>
-    <row r="355" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C355" s="2"/>
     </row>
-    <row r="356" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C356" s="2"/>
     </row>
-    <row r="357" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C357" s="2"/>
     </row>
-    <row r="358" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C358" s="2"/>
     </row>
-    <row r="359" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C359" s="2"/>
     </row>
-    <row r="360" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C360" s="2"/>
     </row>
-    <row r="361" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C361" s="2"/>
     </row>
-    <row r="362" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C362" s="2"/>
     </row>
-    <row r="363" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C363" s="2"/>
     </row>
-    <row r="364" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C364" s="2"/>
     </row>
-    <row r="365" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C365" s="2"/>
     </row>
-    <row r="366" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C366" s="2"/>
     </row>
-    <row r="367" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C367" s="2"/>
     </row>
-    <row r="368" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C368" s="2"/>
     </row>
-    <row r="369" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C369" s="2"/>
     </row>
-    <row r="370" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C370" s="2"/>
     </row>
-    <row r="371" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C371" s="2"/>
     </row>
-    <row r="372" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C372" s="2"/>
     </row>
-    <row r="373" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C373" s="2"/>
     </row>
-    <row r="374" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C374" s="2"/>
     </row>
-    <row r="375" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C375" s="2"/>
     </row>
-    <row r="376" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C376" s="2"/>
     </row>
-    <row r="377" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C377" s="2"/>
     </row>
-    <row r="378" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C378" s="2"/>
     </row>
-    <row r="379" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C379" s="2"/>
     </row>
-    <row r="380" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C380" s="2"/>
     </row>
-    <row r="381" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C381" s="2"/>
     </row>
-    <row r="382" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C382" s="2"/>
     </row>
-    <row r="383" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C383" s="2"/>
     </row>
-    <row r="384" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C384" s="2"/>
     </row>
-    <row r="385" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C385" s="2"/>
     </row>
-    <row r="386" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C386" s="2"/>
     </row>
-    <row r="387" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C387" s="2"/>
     </row>
-    <row r="388" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C388" s="2"/>
     </row>
-    <row r="389" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C389" s="2"/>
     </row>
-    <row r="390" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C390" s="2"/>
     </row>
-    <row r="391" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C391" s="2"/>
     </row>
-    <row r="392" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C392" s="2"/>
     </row>
-    <row r="393" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C393" s="2"/>
     </row>
-    <row r="394" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C394" s="2"/>
     </row>
-    <row r="395" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C395" s="2"/>
     </row>
-    <row r="396" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C396" s="2"/>
     </row>
-    <row r="397" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C397" s="2"/>
     </row>
-    <row r="398" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C398" s="2"/>
     </row>
-    <row r="399" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C399" s="2"/>
     </row>
-    <row r="400" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C400" s="2"/>
     </row>
-    <row r="401" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C401" s="2"/>
     </row>
-    <row r="402" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C402" s="2"/>
     </row>
-    <row r="403" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C403" s="2"/>
     </row>
-    <row r="404" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C404" s="2"/>
     </row>
-    <row r="405" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C405" s="2"/>
     </row>
-    <row r="406" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C406" s="2"/>
     </row>
-    <row r="407" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C407" s="2"/>
     </row>
-    <row r="408" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C408" s="2"/>
     </row>
-    <row r="409" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C409" s="2"/>
     </row>
-    <row r="410" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C410" s="2"/>
     </row>
-    <row r="411" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C411" s="2"/>
     </row>
-    <row r="412" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C412" s="2"/>
     </row>
-    <row r="413" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C413" s="2"/>
     </row>
-    <row r="414" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C414" s="2"/>
     </row>
-    <row r="415" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C415" s="2"/>
     </row>
-    <row r="416" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C416" s="2"/>
     </row>
-    <row r="417" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C417" s="2"/>
     </row>
-    <row r="418" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C418" s="2"/>
     </row>
-    <row r="419" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C419" s="2"/>
     </row>
-    <row r="420" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C420" s="2"/>
     </row>
-    <row r="421" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C421" s="2"/>
     </row>
-    <row r="422" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C422" s="2"/>
     </row>
-    <row r="423" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C423" s="2"/>
     </row>
-    <row r="424" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C424" s="2"/>
     </row>
-    <row r="425" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C425" s="2"/>
     </row>
-    <row r="426" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C426" s="2"/>
     </row>
-    <row r="427" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C427" s="2"/>
     </row>
-    <row r="428" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C428" s="2"/>
     </row>
-    <row r="429" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C429" s="2"/>
     </row>
-    <row r="430" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C430" s="2"/>
     </row>
-    <row r="431" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C431" s="2"/>
     </row>
-    <row r="432" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C432" s="2"/>
     </row>
-    <row r="433" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C433" s="2"/>
     </row>
-    <row r="434" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C434" s="2"/>
     </row>
-    <row r="435" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C435" s="2"/>
     </row>
-    <row r="436" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C436" s="2"/>
     </row>
-    <row r="437" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C437" s="2"/>
     </row>
-    <row r="438" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C438" s="2"/>
     </row>
-    <row r="439" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C439" s="2"/>
     </row>
-    <row r="440" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C440" s="2"/>
     </row>
-    <row r="441" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C441" s="2"/>
     </row>
-    <row r="442" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C442" s="2"/>
     </row>
-    <row r="443" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C443" s="2"/>
     </row>
-    <row r="444" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C444" s="2"/>
     </row>
-    <row r="445" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C445" s="2"/>
     </row>
-    <row r="446" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C446" s="2"/>
     </row>
-    <row r="447" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C447" s="2"/>
     </row>
-    <row r="448" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C448" s="2"/>
     </row>
-    <row r="449" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C449" s="2"/>
     </row>
-    <row r="450" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C450" s="2"/>
     </row>
-    <row r="451" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C451" s="2"/>
     </row>
-    <row r="452" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C452" s="2"/>
     </row>
-    <row r="453" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C453" s="2"/>
     </row>
-    <row r="454" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C454" s="2"/>
     </row>
-    <row r="455" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C455" s="2"/>
     </row>
-    <row r="456" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C456" s="2"/>
     </row>
-    <row r="457" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C457" s="2"/>
     </row>
-    <row r="458" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C458" s="2"/>
     </row>
-    <row r="459" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C459" s="2"/>
     </row>
-    <row r="460" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C460" s="2"/>
     </row>
-    <row r="461" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C461" s="2"/>
     </row>
-    <row r="462" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C462" s="2"/>
     </row>
-    <row r="463" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C463" s="2"/>
     </row>
-    <row r="464" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C464" s="2"/>
     </row>
-    <row r="465" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C465" s="2"/>
     </row>
-    <row r="466" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C466" s="2"/>
     </row>
-    <row r="467" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C467" s="2"/>
     </row>
-    <row r="468" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C468" s="2"/>
     </row>
-    <row r="469" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C469" s="2"/>
     </row>
-    <row r="470" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C470" s="2"/>
     </row>
-    <row r="471" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C471" s="2"/>
     </row>
-    <row r="472" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C472" s="2"/>
     </row>
-    <row r="473" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C473" s="2"/>
     </row>
-    <row r="474" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C474" s="2"/>
     </row>
-    <row r="475" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C475" s="2"/>
     </row>
-    <row r="476" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C476" s="2"/>
     </row>
-    <row r="477" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C477" s="2"/>
     </row>
-    <row r="478" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C478" s="2"/>
     </row>
-    <row r="479" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C479" s="2"/>
     </row>
-    <row r="480" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C480" s="2"/>
     </row>
-    <row r="481" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C481" s="2"/>
     </row>
-    <row r="482" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C482" s="2"/>
     </row>
-    <row r="483" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C483" s="2"/>
     </row>
-    <row r="484" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C484" s="2"/>
     </row>
-    <row r="485" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C485" s="2"/>
     </row>
-    <row r="486" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C486" s="2"/>
     </row>
-    <row r="487" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C487" s="2"/>
     </row>
-    <row r="488" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C488" s="2"/>
     </row>
-    <row r="489" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C489" s="2"/>
     </row>
-    <row r="490" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C490" s="2"/>
     </row>
-    <row r="491" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C491" s="2"/>
     </row>
-    <row r="492" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C492" s="2"/>
     </row>
-    <row r="493" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C493" s="2"/>
     </row>
-    <row r="494" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C494" s="2"/>
     </row>
-    <row r="495" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C495" s="2"/>
     </row>
-    <row r="496" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C496" s="2"/>
     </row>
-    <row r="497" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C497" s="2"/>
     </row>
-    <row r="498" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C498" s="2"/>
     </row>
-    <row r="499" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C499" s="2"/>
     </row>
-    <row r="500" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C500" s="2"/>
     </row>
-    <row r="501" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C501" s="2"/>
     </row>
-    <row r="502" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C502" s="2"/>
     </row>
-    <row r="503" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C503" s="2"/>
     </row>
-    <row r="504" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C504" s="2"/>
     </row>
-    <row r="505" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C505" s="2"/>
     </row>
-    <row r="506" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C506" s="2"/>
     </row>
-    <row r="507" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C507" s="2"/>
     </row>
-    <row r="508" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C508" s="2"/>
     </row>
-    <row r="509" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C509" s="2"/>
     </row>
-    <row r="510" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C510" s="2"/>
     </row>
-    <row r="511" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C511" s="2"/>
     </row>
-    <row r="512" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C512" s="2"/>
     </row>
-    <row r="513" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C513" s="2"/>
     </row>
-    <row r="514" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C514" s="2"/>
     </row>
-    <row r="515" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C515" s="2"/>
     </row>
-    <row r="516" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C516" s="2"/>
     </row>
-    <row r="517" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C517" s="2"/>
     </row>
-    <row r="518" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C518" s="2"/>
     </row>
-    <row r="519" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C519" s="2"/>
     </row>
-    <row r="520" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C520" s="2"/>
     </row>
-    <row r="521" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C521" s="2"/>
     </row>
-    <row r="522" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C522" s="2"/>
     </row>
-    <row r="523" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C523" s="2"/>
     </row>
-    <row r="524" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C524" s="2"/>
     </row>
-    <row r="525" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C525" s="2"/>
     </row>
-    <row r="526" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C526" s="2"/>
     </row>
-    <row r="527" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C527" s="2"/>
     </row>
-    <row r="528" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C528" s="2"/>
     </row>
-    <row r="529" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C529" s="2"/>
     </row>
-    <row r="530" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C530" s="2"/>
     </row>
-    <row r="531" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C531" s="2"/>
     </row>
-    <row r="532" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C532" s="2"/>
     </row>
-    <row r="533" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C533" s="2"/>
     </row>
-    <row r="534" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C534" s="2"/>
     </row>
-    <row r="535" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C535" s="2"/>
     </row>
-    <row r="536" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C536" s="2"/>
     </row>
-    <row r="537" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C537" s="2"/>
     </row>
-    <row r="538" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C538" s="2"/>
     </row>
-    <row r="539" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C539" s="2"/>
     </row>
-    <row r="540" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C540" s="2"/>
     </row>
-    <row r="541" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C541" s="2"/>
     </row>
-    <row r="542" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C542" s="2"/>
     </row>
-    <row r="543" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C543" s="2"/>
     </row>
-    <row r="544" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C544" s="2"/>
     </row>
-    <row r="545" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="545" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C545" s="2"/>
     </row>
-    <row r="546" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C546" s="2"/>
     </row>
-    <row r="547" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C547" s="2"/>
     </row>
-    <row r="548" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="548" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C548" s="2"/>
     </row>
-    <row r="549" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="549" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C549" s="2"/>
     </row>
-    <row r="550" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="550" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C550" s="2"/>
     </row>
-    <row r="551" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="551" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C551" s="2"/>
     </row>
-    <row r="552" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="552" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C552" s="2"/>
     </row>
-    <row r="553" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="553" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C553" s="2"/>
     </row>
-    <row r="554" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="554" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C554" s="2"/>
     </row>
-    <row r="555" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="555" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C555" s="2"/>
     </row>
-    <row r="556" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="556" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C556" s="2"/>
     </row>
-    <row r="557" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="557" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C557" s="2"/>
     </row>
-    <row r="558" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C558" s="2"/>
     </row>
-    <row r="559" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C559" s="2"/>
     </row>
-    <row r="560" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="560" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C560" s="2"/>
     </row>
-    <row r="561" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="561" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C561" s="2"/>
     </row>
-    <row r="562" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="562" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C562" s="2"/>
     </row>
-    <row r="563" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="563" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C563" s="2"/>
     </row>
-    <row r="564" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="564" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C564" s="2"/>
     </row>
-    <row r="565" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="565" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C565" s="2"/>
     </row>
-    <row r="566" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="566" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C566" s="2"/>
     </row>
-    <row r="567" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="567" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C567" s="2"/>
     </row>
-    <row r="568" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="568" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C568" s="2"/>
     </row>
-    <row r="569" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="569" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C569" s="2"/>
     </row>
-    <row r="570" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="570" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C570" s="2"/>
     </row>
-    <row r="571" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="571" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C571" s="2"/>
     </row>
-    <row r="572" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="572" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C572" s="2"/>
     </row>
-    <row r="573" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="573" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C573" s="2"/>
     </row>
-    <row r="574" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="574" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C574" s="2"/>
     </row>
-    <row r="575" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C575" s="2"/>
     </row>
-    <row r="576" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="576" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C576" s="2"/>
     </row>
-    <row r="577" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="577" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C577" s="2"/>
     </row>
-    <row r="578" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="578" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C578" s="2"/>
     </row>
-    <row r="579" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="579" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C579" s="2"/>
     </row>
-    <row r="580" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="580" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C580" s="2"/>
     </row>
-    <row r="581" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="581" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C581" s="2"/>
     </row>
-    <row r="582" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="582" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C582" s="2"/>
     </row>
-    <row r="583" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="583" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C583" s="2"/>
     </row>
-    <row r="584" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="584" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C584" s="2"/>
     </row>
-    <row r="585" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="585" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C585" s="2"/>
     </row>
-    <row r="586" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="586" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C586" s="2"/>
     </row>
-    <row r="587" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="587" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C587" s="2"/>
     </row>
-    <row r="588" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="588" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C588" s="2"/>
     </row>
-    <row r="589" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="589" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C589" s="2"/>
     </row>
-    <row r="590" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="590" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C590" s="2"/>
     </row>
-    <row r="591" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="591" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C591" s="2"/>
     </row>
-    <row r="592" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="592" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C592" s="2"/>
     </row>
-    <row r="593" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="593" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C593" s="2"/>
     </row>
-    <row r="594" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="594" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C594" s="2"/>
     </row>
-    <row r="595" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="595" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C595" s="2"/>
     </row>
-    <row r="596" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="596" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C596" s="2"/>
     </row>
-    <row r="597" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="597" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C597" s="2"/>
     </row>
-    <row r="598" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="598" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C598" s="2"/>
     </row>
-    <row r="599" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="599" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C599" s="2"/>
     </row>
-    <row r="600" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="600" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C600" s="2"/>
     </row>
-    <row r="601" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="601" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C601" s="2"/>
     </row>
-    <row r="602" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="602" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C602" s="2"/>
     </row>
-    <row r="603" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="603" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C603" s="2"/>
     </row>
-    <row r="604" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="604" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C604" s="2"/>
     </row>
-    <row r="605" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="605" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C605" s="2"/>
     </row>
-    <row r="606" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="606" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C606" s="2"/>
     </row>
-    <row r="607" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="607" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C607" s="2"/>
     </row>
-    <row r="608" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="608" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C608" s="2"/>
     </row>
-    <row r="609" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="609" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C609" s="2"/>
     </row>
-    <row r="610" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="610" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C610" s="2"/>
     </row>
-    <row r="611" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="611" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C611" s="2"/>
     </row>
-    <row r="612" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="612" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C612" s="2"/>
     </row>
-    <row r="613" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="613" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C613" s="2"/>
     </row>
-    <row r="614" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="614" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C614" s="2"/>
     </row>
-    <row r="615" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="615" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C615" s="2"/>
     </row>
-    <row r="616" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="616" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C616" s="2"/>
     </row>
-    <row r="617" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="617" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C617" s="2"/>
     </row>
-    <row r="618" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="618" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C618" s="2"/>
     </row>
-    <row r="619" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="619" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C619" s="2"/>
     </row>
-    <row r="620" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="620" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C620" s="2"/>
     </row>
-    <row r="621" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="621" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C621" s="2"/>
     </row>
-    <row r="622" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="622" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C622" s="2"/>
     </row>
-    <row r="623" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="623" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C623" s="2"/>
     </row>
-    <row r="624" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="624" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C624" s="2"/>
     </row>
-    <row r="625" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="625" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C625" s="2"/>
     </row>
-    <row r="626" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="626" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C626" s="2"/>
     </row>
-    <row r="627" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="627" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C627" s="2"/>
     </row>
-    <row r="628" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="628" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C628" s="2"/>
     </row>
-    <row r="629" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="629" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C629" s="2"/>
     </row>
-    <row r="630" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="630" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C630" s="2"/>
     </row>
-    <row r="631" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="631" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C631" s="2"/>
     </row>
-    <row r="632" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="632" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C632" s="2"/>
     </row>
-    <row r="633" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="633" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C633" s="2"/>
     </row>
-    <row r="634" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="634" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C634" s="2"/>
     </row>
-    <row r="635" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="635" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C635" s="2"/>
     </row>
-    <row r="636" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="636" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C636" s="2"/>
     </row>
-    <row r="637" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="637" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C637" s="2"/>
     </row>
-    <row r="638" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="638" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C638" s="2"/>
     </row>
-    <row r="639" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="639" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C639" s="2"/>
     </row>
-    <row r="640" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="640" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C640" s="2"/>
     </row>
-    <row r="641" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="641" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C641" s="2"/>
     </row>
-    <row r="642" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="642" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C642" s="2"/>
     </row>
-    <row r="643" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="643" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C643" s="2"/>
     </row>
-    <row r="644" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="644" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C644" s="2"/>
     </row>
-    <row r="645" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="645" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C645" s="2"/>
     </row>
-    <row r="646" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="646" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C646" s="2"/>
     </row>
-    <row r="647" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="647" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C647" s="2"/>
     </row>
-    <row r="648" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="648" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C648" s="2"/>
     </row>
-    <row r="649" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="649" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C649" s="2"/>
     </row>
-    <row r="650" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="650" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C650" s="2"/>
     </row>
-    <row r="651" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="651" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C651" s="2"/>
     </row>
-    <row r="652" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="652" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C652" s="2"/>
     </row>
-    <row r="653" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="653" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C653" s="2"/>
     </row>
-    <row r="654" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="654" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C654" s="2"/>
     </row>
-    <row r="655" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="655" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C655" s="2"/>
     </row>
-    <row r="656" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="656" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C656" s="2"/>
     </row>
-    <row r="657" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="657" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C657" s="2"/>
     </row>
-    <row r="658" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="658" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C658" s="2"/>
     </row>
-    <row r="659" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="659" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C659" s="2"/>
     </row>
-    <row r="660" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="660" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C660" s="2"/>
     </row>
-    <row r="661" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="661" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C661" s="2"/>
     </row>
-    <row r="662" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="662" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C662" s="2"/>
     </row>
-    <row r="663" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="663" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C663" s="2"/>
     </row>
-    <row r="664" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="664" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C664" s="2"/>
     </row>
-    <row r="665" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="665" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C665" s="2"/>
     </row>
-    <row r="666" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="666" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C666" s="2"/>
     </row>
-    <row r="667" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="667" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C667" s="2"/>
     </row>
-    <row r="668" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="668" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C668" s="2"/>
     </row>
-    <row r="669" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="669" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C669" s="2"/>
     </row>
-    <row r="670" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="670" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C670" s="2"/>
     </row>
-    <row r="671" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="671" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C671" s="2"/>
     </row>
-    <row r="672" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="672" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C672" s="2"/>
     </row>
-    <row r="673" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="673" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C673" s="2"/>
     </row>
-    <row r="674" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="674" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C674" s="2"/>
     </row>
-    <row r="675" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="675" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C675" s="2"/>
     </row>
-    <row r="676" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="676" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C676" s="2"/>
     </row>
-    <row r="677" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="677" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C677" s="2"/>
     </row>
-    <row r="678" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="678" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C678" s="2"/>
     </row>
-    <row r="679" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="679" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C679" s="2"/>
     </row>
-    <row r="680" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="680" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C680" s="2"/>
     </row>
-    <row r="681" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="681" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C681" s="2"/>
     </row>
-    <row r="682" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="682" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C682" s="2"/>
     </row>
-    <row r="683" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="683" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C683" s="2"/>
     </row>
-    <row r="684" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="684" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C684" s="2"/>
     </row>
-    <row r="685" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="685" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C685" s="2"/>
     </row>
-    <row r="686" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="686" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C686" s="2"/>
     </row>
-    <row r="687" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="687" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C687" s="2"/>
     </row>
-    <row r="688" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="688" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C688" s="2"/>
     </row>
-    <row r="689" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="689" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C689" s="2"/>
     </row>
-    <row r="690" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="690" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C690" s="2"/>
     </row>
-    <row r="691" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="691" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C691" s="2"/>
     </row>
-    <row r="692" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="692" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C692" s="2"/>
     </row>
-    <row r="693" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="693" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C693" s="2"/>
     </row>
-    <row r="694" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="694" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C694" s="2"/>
     </row>
-    <row r="695" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="695" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C695" s="2"/>
     </row>
-    <row r="696" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="696" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C696" s="2"/>
     </row>
-    <row r="697" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="697" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C697" s="2"/>
     </row>
-    <row r="698" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="698" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C698" s="2"/>
     </row>
-    <row r="699" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="699" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C699" s="2"/>
     </row>
-    <row r="700" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="700" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C700" s="2"/>
     </row>
-    <row r="701" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="701" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C701" s="2"/>
     </row>
-    <row r="702" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="702" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C702" s="2"/>
     </row>
-    <row r="703" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="703" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C703" s="2"/>
     </row>
-    <row r="704" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="704" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C704" s="2"/>
     </row>
-    <row r="705" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="705" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C705" s="2"/>
     </row>
-    <row r="706" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="706" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C706" s="2"/>
     </row>
-    <row r="707" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="707" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C707" s="2"/>
     </row>
-    <row r="708" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="708" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C708" s="2"/>
     </row>
-    <row r="709" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="709" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C709" s="2"/>
     </row>
-    <row r="710" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="710" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C710" s="2"/>
     </row>
-    <row r="711" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="711" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C711" s="2"/>
     </row>
-    <row r="712" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="712" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C712" s="2"/>
     </row>
-    <row r="713" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="713" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C713" s="2"/>
     </row>
-    <row r="714" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="714" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C714" s="2"/>
     </row>
-    <row r="715" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="715" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C715" s="2"/>
     </row>
-    <row r="716" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="716" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C716" s="2"/>
     </row>
-    <row r="717" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="717" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C717" s="2"/>
     </row>
-    <row r="718" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="718" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C718" s="2"/>
     </row>
-    <row r="719" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="719" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C719" s="2"/>
     </row>
-    <row r="720" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="720" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C720" s="2"/>
     </row>
-    <row r="721" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="721" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C721" s="2"/>
     </row>
-    <row r="722" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="722" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C722" s="2"/>
     </row>
-    <row r="723" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="723" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C723" s="2"/>
     </row>
-    <row r="724" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="724" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C724" s="2"/>
     </row>
-    <row r="725" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="725" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C725" s="2"/>
     </row>
-    <row r="726" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="726" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C726" s="2"/>
     </row>
-    <row r="727" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="727" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C727" s="2"/>
     </row>
-    <row r="728" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="728" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C728" s="2"/>
     </row>
-    <row r="729" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="729" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C729" s="2"/>
     </row>
-    <row r="730" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="730" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C730" s="2"/>
     </row>
-    <row r="731" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="731" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C731" s="2"/>
     </row>
-    <row r="732" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="732" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C732" s="2"/>
     </row>
-    <row r="733" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="733" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C733" s="2"/>
     </row>
-    <row r="734" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="734" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C734" s="2"/>
     </row>
-    <row r="735" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="735" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C735" s="2"/>
     </row>
-    <row r="736" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="736" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C736" s="2"/>
     </row>
-    <row r="737" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="737" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C737" s="2"/>
     </row>
-    <row r="738" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="738" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C738" s="2"/>
     </row>
-    <row r="739" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="739" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C739" s="2"/>
     </row>
-    <row r="740" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="740" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C740" s="2"/>
     </row>
-    <row r="741" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="741" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C741" s="2"/>
     </row>
-    <row r="742" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="742" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C742" s="2"/>
     </row>
-    <row r="743" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="743" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C743" s="2"/>
     </row>
-    <row r="744" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="744" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C744" s="2"/>
     </row>
-    <row r="745" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="745" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C745" s="2"/>
     </row>
-    <row r="746" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="746" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C746" s="2"/>
     </row>
-    <row r="747" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="747" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C747" s="2"/>
     </row>
-    <row r="748" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="748" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C748" s="2"/>
     </row>
-    <row r="749" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="749" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C749" s="2"/>
     </row>
-    <row r="750" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="750" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C750" s="2"/>
     </row>
-    <row r="751" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="751" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C751" s="2"/>
     </row>
-    <row r="752" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="752" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C752" s="2"/>
     </row>
-    <row r="753" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="753" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C753" s="2"/>
     </row>
-    <row r="754" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="754" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C754" s="2"/>
     </row>
-    <row r="755" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="755" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C755" s="2"/>
     </row>
-    <row r="756" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="756" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C756" s="2"/>
     </row>
-    <row r="757" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="757" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C757" s="2"/>
     </row>
-    <row r="758" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="758" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C758" s="2"/>
     </row>
-    <row r="759" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="759" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C759" s="2"/>
     </row>
-    <row r="760" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="760" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C760" s="2"/>
     </row>
-    <row r="761" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="761" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C761" s="2"/>
     </row>
-    <row r="762" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="762" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C762" s="2"/>
     </row>
-    <row r="763" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="763" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C763" s="2"/>
     </row>
-    <row r="764" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="764" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C764" s="2"/>
     </row>
-    <row r="765" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="765" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C765" s="2"/>
     </row>
-    <row r="766" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="766" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C766" s="2"/>
     </row>
-    <row r="767" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="767" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C767" s="2"/>
     </row>
-    <row r="768" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="768" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C768" s="2"/>
     </row>
-    <row r="769" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="769" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C769" s="2"/>
     </row>
-    <row r="770" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="770" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C770" s="2"/>
     </row>
-    <row r="771" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="771" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C771" s="2"/>
     </row>
-    <row r="772" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="772" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C772" s="2"/>
     </row>
-    <row r="773" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="773" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C773" s="2"/>
     </row>
-    <row r="774" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="774" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C774" s="2"/>
     </row>
-    <row r="775" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="775" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C775" s="2"/>
     </row>
-    <row r="776" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="776" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C776" s="2"/>
     </row>
-    <row r="777" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="777" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C777" s="2"/>
     </row>
-    <row r="778" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="778" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C778" s="2"/>
     </row>
-    <row r="779" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="779" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C779" s="2"/>
     </row>
-    <row r="780" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="780" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C780" s="2"/>
     </row>
-    <row r="781" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="781" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C781" s="2"/>
     </row>
-    <row r="782" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="782" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C782" s="2"/>
     </row>
-    <row r="783" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="783" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C783" s="2"/>
     </row>
-    <row r="784" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="784" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C784" s="2"/>
     </row>
-    <row r="785" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="785" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C785" s="2"/>
     </row>
-    <row r="786" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="786" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C786" s="2"/>
     </row>
-    <row r="787" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="787" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C787" s="2"/>
     </row>
-    <row r="788" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="788" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C788" s="2"/>
     </row>
-    <row r="789" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="789" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C789" s="2"/>
     </row>
-    <row r="790" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="790" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C790" s="2"/>
     </row>
-    <row r="791" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="791" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C791" s="2"/>
     </row>
-    <row r="792" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="792" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C792" s="2"/>
     </row>
-    <row r="793" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="793" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C793" s="2"/>
     </row>
-    <row r="794" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="794" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C794" s="2"/>
     </row>
-    <row r="795" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="795" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C795" s="2"/>
     </row>
-    <row r="796" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="796" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C796" s="2"/>
     </row>
-    <row r="797" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="797" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C797" s="2"/>
     </row>
-    <row r="798" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="798" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C798" s="2"/>
     </row>
-    <row r="799" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="799" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C799" s="2"/>
     </row>
-    <row r="800" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="800" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C800" s="2"/>
     </row>
-    <row r="801" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="801" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C801" s="2"/>
     </row>
-    <row r="802" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="802" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C802" s="2"/>
     </row>
-    <row r="803" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="803" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C803" s="2"/>
     </row>
-    <row r="804" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="804" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C804" s="2"/>
     </row>
-    <row r="805" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="805" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C805" s="2"/>
     </row>
-    <row r="806" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="806" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C806" s="2"/>
     </row>
-    <row r="807" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="807" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C807" s="2"/>
     </row>
-    <row r="808" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="808" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C808" s="2"/>
     </row>
-    <row r="809" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="809" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C809" s="2"/>
     </row>
-    <row r="810" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="810" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C810" s="2"/>
     </row>
-    <row r="811" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="811" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C811" s="2"/>
     </row>
-    <row r="812" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="812" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C812" s="2"/>
     </row>
-    <row r="813" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="813" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C813" s="2"/>
     </row>
-    <row r="814" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="814" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C814" s="2"/>
     </row>
-    <row r="815" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="815" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C815" s="2"/>
     </row>
-    <row r="816" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="816" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C816" s="2"/>
     </row>
-    <row r="817" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="817" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C817" s="2"/>
     </row>
-    <row r="818" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="818" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C818" s="2"/>
     </row>
-    <row r="819" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="819" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C819" s="2"/>
     </row>
-    <row r="820" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="820" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C820" s="2"/>
     </row>
-    <row r="821" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="821" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C821" s="2"/>
     </row>
-    <row r="822" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="822" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C822" s="2"/>
     </row>
-    <row r="823" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="823" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C823" s="2"/>
     </row>
-    <row r="824" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="824" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C824" s="2"/>
     </row>
-    <row r="825" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="825" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C825" s="2"/>
     </row>
-    <row r="826" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="826" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C826" s="2"/>
     </row>
-    <row r="827" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="827" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C827" s="2"/>
     </row>
-    <row r="828" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="828" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C828" s="2"/>
     </row>
-    <row r="829" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="829" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C829" s="2"/>
     </row>
-    <row r="830" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="830" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C830" s="2"/>
     </row>
-    <row r="831" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="831" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C831" s="2"/>
     </row>
-    <row r="832" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="832" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C832" s="2"/>
     </row>
-    <row r="833" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="833" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C833" s="2"/>
     </row>
-    <row r="834" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="834" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C834" s="2"/>
     </row>
-    <row r="835" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="835" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C835" s="2"/>
     </row>
-    <row r="836" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="836" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C836" s="2"/>
     </row>
-    <row r="837" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="837" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C837" s="2"/>
     </row>
-    <row r="838" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="838" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C838" s="2"/>
     </row>
-    <row r="839" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="839" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C839" s="2"/>
     </row>
-    <row r="840" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="840" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C840" s="2"/>
     </row>
-    <row r="841" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="841" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C841" s="2"/>
     </row>
-    <row r="842" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="842" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C842" s="2"/>
     </row>
-    <row r="843" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="843" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C843" s="2"/>
     </row>
-    <row r="844" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="844" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C844" s="2"/>
     </row>
-    <row r="845" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="845" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C845" s="2"/>
     </row>
-    <row r="846" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="846" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C846" s="2"/>
     </row>
-    <row r="847" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="847" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C847" s="2"/>
     </row>
-    <row r="848" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="848" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C848" s="2"/>
     </row>
-    <row r="849" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="849" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C849" s="2"/>
     </row>
-    <row r="850" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="850" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C850" s="2"/>
     </row>
-    <row r="851" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="851" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C851" s="2"/>
     </row>
-    <row r="852" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="852" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C852" s="2"/>
     </row>
-    <row r="853" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="853" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C853" s="2"/>
     </row>
-    <row r="854" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="854" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C854" s="2"/>
     </row>
-    <row r="855" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="855" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C855" s="2"/>
     </row>
-    <row r="856" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="856" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C856" s="2"/>
     </row>
-    <row r="857" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="857" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C857" s="2"/>
     </row>
-    <row r="858" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="858" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C858" s="2"/>
     </row>
-    <row r="859" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="859" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C859" s="2"/>
     </row>
-    <row r="860" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="860" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C860" s="2"/>
     </row>
-    <row r="861" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="861" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C861" s="2"/>
     </row>
-    <row r="862" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="862" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C862" s="2"/>
     </row>
-    <row r="863" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="863" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C863" s="2"/>
     </row>
-    <row r="864" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="864" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C864" s="2"/>
     </row>
-    <row r="865" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="865" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C865" s="2"/>
     </row>
-    <row r="866" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="866" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C866" s="2"/>
     </row>
-    <row r="867" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="867" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C867" s="2"/>
     </row>
-    <row r="868" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="868" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C868" s="2"/>
     </row>
-    <row r="869" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="869" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C869" s="2"/>
     </row>
-    <row r="870" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="870" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C870" s="2"/>
     </row>
-    <row r="871" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="871" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C871" s="2"/>
     </row>
-    <row r="872" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="872" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C872" s="2"/>
     </row>
-    <row r="873" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="873" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C873" s="2"/>
     </row>
-    <row r="874" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="874" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C874" s="2"/>
     </row>
-    <row r="875" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="875" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C875" s="2"/>
     </row>
-    <row r="876" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="876" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C876" s="2"/>
     </row>
-    <row r="877" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="877" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C877" s="2"/>
     </row>
-    <row r="878" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="878" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C878" s="2"/>
     </row>
-    <row r="879" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="879" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C879" s="2"/>
     </row>
-    <row r="880" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="880" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C880" s="2"/>
     </row>
-    <row r="881" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="881" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C881" s="2"/>
     </row>
-    <row r="882" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="882" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C882" s="2"/>
     </row>
-    <row r="883" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="883" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C883" s="2"/>
     </row>
-    <row r="884" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="884" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C884" s="2"/>
     </row>
-    <row r="885" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="885" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C885" s="2"/>
     </row>
-    <row r="886" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="886" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C886" s="2"/>
     </row>
-    <row r="887" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="887" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C887" s="2"/>
     </row>
-    <row r="888" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="888" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C888" s="2"/>
     </row>
-    <row r="889" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="889" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C889" s="2"/>
     </row>
-    <row r="890" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="890" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C890" s="2"/>
     </row>
-    <row r="891" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="891" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C891" s="2"/>
     </row>
-    <row r="892" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="892" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C892" s="2"/>
     </row>
-    <row r="893" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="893" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C893" s="2"/>
     </row>
-    <row r="894" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="894" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C894" s="2"/>
     </row>
-    <row r="895" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="895" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C895" s="2"/>
     </row>
-    <row r="896" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="896" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C896" s="2"/>
     </row>
-    <row r="897" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="897" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C897" s="2"/>
     </row>
-    <row r="898" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="898" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C898" s="2"/>
     </row>
-    <row r="899" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="899" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C899" s="2"/>
     </row>
-    <row r="900" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="900" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C900" s="2"/>
     </row>
-    <row r="901" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="901" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C901" s="2"/>
     </row>
-    <row r="902" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="902" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C902" s="2"/>
     </row>
-    <row r="903" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="903" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C903" s="2"/>
     </row>
-    <row r="904" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="904" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C904" s="2"/>
     </row>
-    <row r="905" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="905" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C905" s="2"/>
     </row>
-    <row r="906" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="906" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C906" s="2"/>
     </row>
-    <row r="907" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="907" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C907" s="2"/>
     </row>
-    <row r="908" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="908" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C908" s="2"/>
     </row>
-    <row r="909" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="909" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C909" s="2"/>
     </row>
-    <row r="910" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="910" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C910" s="2"/>
     </row>
-    <row r="911" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="911" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C911" s="2"/>
     </row>
-    <row r="912" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="912" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C912" s="2"/>
     </row>
-    <row r="913" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="913" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C913" s="2"/>
     </row>
-    <row r="914" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="914" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C914" s="2"/>
     </row>
-    <row r="915" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="915" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C915" s="2"/>
     </row>
-    <row r="916" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="916" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C916" s="2"/>
     </row>
-    <row r="917" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="917" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C917" s="2"/>
     </row>
-    <row r="918" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="918" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C918" s="2"/>
     </row>
-    <row r="919" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="919" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C919" s="2"/>
     </row>
-    <row r="920" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="920" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C920" s="2"/>
     </row>
-    <row r="921" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="921" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C921" s="2"/>
     </row>
-    <row r="922" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="922" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C922" s="2"/>
     </row>
-    <row r="923" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="923" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C923" s="2"/>
     </row>
-    <row r="924" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="924" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C924" s="2"/>
     </row>
-    <row r="925" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="925" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C925" s="2"/>
     </row>
-    <row r="926" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="926" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C926" s="2"/>
     </row>
-    <row r="927" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="927" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C927" s="2"/>
     </row>
-    <row r="928" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="928" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C928" s="2"/>
     </row>
-    <row r="929" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="929" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C929" s="2"/>
     </row>
-    <row r="930" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="930" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C930" s="2"/>
     </row>
-    <row r="931" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="931" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C931" s="2"/>
     </row>
-    <row r="932" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="932" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C932" s="2"/>
     </row>
-    <row r="933" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="933" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C933" s="2"/>
     </row>
-    <row r="934" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="934" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C934" s="2"/>
     </row>
-    <row r="935" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="935" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C935" s="2"/>
     </row>
-    <row r="936" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="936" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C936" s="2"/>
     </row>
-    <row r="937" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="937" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C937" s="2"/>
     </row>
-    <row r="938" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="938" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C938" s="2"/>
     </row>
-    <row r="939" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="939" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C939" s="2"/>
     </row>
-    <row r="940" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="940" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C940" s="2"/>
     </row>
-    <row r="941" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="941" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C941" s="2"/>
     </row>
-    <row r="942" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="942" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C942" s="2"/>
     </row>
-    <row r="943" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="943" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C943" s="2"/>
     </row>
-    <row r="944" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="944" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C944" s="2"/>
     </row>
-    <row r="945" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="945" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C945" s="2"/>
     </row>
-    <row r="946" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="946" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C946" s="2"/>
     </row>
-    <row r="947" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="947" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C947" s="2"/>
     </row>
-    <row r="948" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="948" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C948" s="2"/>
     </row>
-    <row r="949" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="949" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C949" s="2"/>
     </row>
-    <row r="950" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="950" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C950" s="2"/>
     </row>
-    <row r="951" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="951" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C951" s="2"/>
     </row>
-    <row r="952" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="952" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C952" s="2"/>
     </row>
-    <row r="953" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="953" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C953" s="2"/>
     </row>
-    <row r="954" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="954" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C954" s="2"/>
     </row>
-    <row r="955" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="955" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C955" s="2"/>
     </row>
-    <row r="956" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="956" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C956" s="2"/>
     </row>
-    <row r="957" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="957" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C957" s="2"/>
     </row>
-    <row r="958" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="958" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C958" s="2"/>
     </row>
-    <row r="959" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="959" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C959" s="2"/>
     </row>
-    <row r="960" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="960" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C960" s="2"/>
     </row>
-    <row r="961" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="961" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C961" s="2"/>
     </row>
-    <row r="962" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="962" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C962" s="2"/>
     </row>
-    <row r="963" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="963" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C963" s="2"/>
     </row>
-    <row r="964" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="964" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C964" s="2"/>
     </row>
-    <row r="965" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="965" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C965" s="2"/>
     </row>
-    <row r="966" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="966" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C966" s="2"/>
     </row>
-    <row r="967" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="967" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C967" s="2"/>
     </row>
-    <row r="968" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="968" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C968" s="2"/>
     </row>
-    <row r="969" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="969" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C969" s="2"/>
     </row>
-    <row r="970" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="970" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C970" s="2"/>
     </row>
-    <row r="971" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="971" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C971" s="2"/>
     </row>
-    <row r="972" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="972" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C972" s="2"/>
     </row>
-    <row r="973" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="973" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C973" s="2"/>
     </row>
-    <row r="974" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="974" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C974" s="2"/>
     </row>
-    <row r="975" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="975" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C975" s="2"/>
     </row>
-    <row r="976" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="976" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C976" s="2"/>
     </row>
-    <row r="977" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="977" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C977" s="2"/>
     </row>
-    <row r="978" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="978" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C978" s="2"/>
     </row>
-    <row r="979" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="979" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C979" s="2"/>
     </row>
-    <row r="980" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="980" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C980" s="2"/>
     </row>
-    <row r="981" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="981" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C981" s="2"/>
     </row>
-    <row r="982" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="982" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C982" s="2"/>
     </row>
-    <row r="983" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="983" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C983" s="2"/>
     </row>
-    <row r="984" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="984" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C984" s="2"/>
     </row>
-    <row r="985" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="985" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C985" s="2"/>
     </row>
-    <row r="986" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="986" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C986" s="2"/>
     </row>
-    <row r="987" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="987" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C987" s="2"/>
     </row>
-    <row r="988" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="988" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C988" s="2"/>
     </row>
-    <row r="989" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="989" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C989" s="2"/>
     </row>
-    <row r="990" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="990" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C990" s="2"/>
     </row>
-    <row r="991" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="991" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C991" s="2"/>
     </row>
-    <row r="992" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="992" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C992" s="2"/>
     </row>
-    <row r="993" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="993" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C993" s="2"/>
     </row>
-    <row r="994" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="994" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C994" s="2"/>
     </row>
-    <row r="995" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="995" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C995" s="2"/>
     </row>
-    <row r="996" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="996" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C996" s="2"/>
     </row>
-    <row r="997" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="997" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C997" s="2"/>
     </row>
-    <row r="998" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="998" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C998" s="2"/>
     </row>
-    <row r="999" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="999" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C999" s="2"/>
     </row>
-    <row r="1000" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1000" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1000" s="2"/>
     </row>
-    <row r="1001" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1001" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1001" s="2"/>
     </row>
-    <row r="1002" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1002" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1002" s="2"/>
     </row>
-    <row r="1003" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1003" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1003" s="2"/>
     </row>
-    <row r="1004" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1004" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1004" s="2"/>
     </row>
-    <row r="1005" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1005" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1005" s="2"/>
     </row>
-    <row r="1006" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1006" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1006" s="2"/>
     </row>
-    <row r="1007" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1007" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1007" s="2"/>
     </row>
-    <row r="1008" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1008" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1008" s="2"/>
     </row>
-    <row r="1009" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1009" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1009" s="2"/>
     </row>
-    <row r="1010" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1010" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1010" s="2"/>
     </row>
-    <row r="1011" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1011" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1011" s="2"/>
     </row>
-    <row r="1012" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1012" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1012" s="2"/>
     </row>
-    <row r="1013" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1013" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1013" s="2"/>
     </row>
-    <row r="1014" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1014" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1014" s="2"/>
     </row>
-    <row r="1015" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1015" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1015" s="2"/>
     </row>
-    <row r="1016" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1016" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1016" s="2"/>
     </row>
-    <row r="1017" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1017" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1017" s="2"/>
     </row>
-    <row r="1018" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1018" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1018" s="2"/>
     </row>
-    <row r="1019" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1019" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1019" s="2"/>
     </row>
-    <row r="1020" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1020" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1020" s="2"/>
     </row>
-    <row r="1021" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1021" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1021" s="2"/>
     </row>
-    <row r="1022" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1022" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1022" s="2"/>
     </row>
-    <row r="1023" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1023" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1023" s="2"/>
     </row>
-    <row r="1024" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1024" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1024" s="2"/>
     </row>
-    <row r="1025" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1025" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1025" s="2"/>
     </row>
-    <row r="1026" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1026" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1026" s="2"/>
     </row>
-    <row r="1027" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1027" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1027" s="2"/>
     </row>
-    <row r="1028" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1028" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1028" s="2"/>
     </row>
-    <row r="1029" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1029" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1029" s="2"/>
     </row>
-    <row r="1030" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1030" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1030" s="2"/>
     </row>
-    <row r="1031" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1031" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1031" s="2"/>
     </row>
-    <row r="1032" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1032" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1032" s="2"/>
     </row>
-    <row r="1033" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1033" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1033" s="2"/>
     </row>
-    <row r="1034" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1034" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1034" s="2"/>
     </row>
-    <row r="1035" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1035" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1035" s="2"/>
     </row>
-    <row r="1036" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1036" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1036" s="2"/>
     </row>
-    <row r="1037" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1037" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1037" s="2"/>
     </row>
-    <row r="1038" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1038" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1038" s="2"/>
     </row>
-    <row r="1039" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1039" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1039" s="2"/>
     </row>
-    <row r="1040" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1040" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1040" s="2"/>
     </row>
-    <row r="1041" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1041" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1041" s="2"/>
     </row>
-    <row r="1042" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1042" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1042" s="2"/>
     </row>
-    <row r="1043" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1043" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1043" s="2"/>
     </row>
-    <row r="1044" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1044" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1044" s="2"/>
     </row>
-    <row r="1045" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1045" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1045" s="2"/>
     </row>
-    <row r="1046" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1046" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1046" s="2"/>
     </row>
-    <row r="1047" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1047" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1047" s="2"/>
     </row>
-    <row r="1048" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1048" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1048" s="2"/>
     </row>
-    <row r="1049" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1049" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1049" s="2"/>
     </row>
-    <row r="1050" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1050" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1050" s="2"/>
     </row>
-    <row r="1051" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1051" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1051" s="2"/>
     </row>
-    <row r="1052" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1052" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1052" s="2"/>
     </row>
-    <row r="1053" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1053" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1053" s="2"/>
     </row>
-    <row r="1054" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1054" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1054" s="2"/>
     </row>
-    <row r="1055" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1055" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1055" s="2"/>
     </row>
-    <row r="1056" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1056" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1056" s="2"/>
     </row>
-    <row r="1057" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1057" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1057" s="2"/>
     </row>
-    <row r="1058" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1058" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1058" s="2"/>
     </row>
-    <row r="1059" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1059" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1059" s="2"/>
     </row>
-    <row r="1060" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1060" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1060" s="2"/>
     </row>
-    <row r="1061" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1061" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1061" s="2"/>
     </row>
-    <row r="1062" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1062" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1062" s="2"/>
     </row>
-    <row r="1063" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1063" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1063" s="2"/>
     </row>
-    <row r="1064" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1064" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1064" s="2"/>
     </row>
-    <row r="1065" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1065" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1065" s="2"/>
     </row>
-    <row r="1066" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1066" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1066" s="2"/>
     </row>
-    <row r="1067" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1067" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1067" s="2"/>
     </row>
-    <row r="1068" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1068" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1068" s="2"/>
     </row>
-    <row r="1069" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1069" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1069" s="2"/>
     </row>
-    <row r="1070" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1070" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1070" s="2"/>
     </row>
-    <row r="1071" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1071" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1071" s="2"/>
     </row>
-    <row r="1072" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1072" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1072" s="2"/>
     </row>
-    <row r="1073" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1073" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1073" s="2"/>
     </row>
-    <row r="1074" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1074" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1074" s="2"/>
     </row>
-    <row r="1075" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1075" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1075" s="2"/>
     </row>
-    <row r="1076" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1076" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1076" s="2"/>
     </row>
-    <row r="1077" s="15" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1077" s="8" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C1077" s="2"/>
     </row>
   </sheetData>
